--- a/calculation_python/outputs/Results_final.xlsx
+++ b/calculation_python/outputs/Results_final.xlsx
@@ -9529,7 +9529,7 @@
         <v>-81.344481801271</v>
       </c>
       <c r="C123">
-        <v>95.39821916139468</v>
+        <v>394.8659066068382</v>
       </c>
       <c r="D123" s="3">
         <v>0.7818454474839299</v>
@@ -9548,7 +9548,7 @@
         <v>-26.76457855379006</v>
       </c>
       <c r="H123">
-        <v>95.39821916139468</v>
+        <v>394.8659066068382</v>
       </c>
       <c r="I123" s="2">
         <v>2.3762306828947644</v>
@@ -9599,7 +9599,7 @@
         <v>-90.83144995136678</v>
       </c>
       <c r="C124">
-        <v>95.39821916139468</v>
+        <v>394.8659066068382</v>
       </c>
       <c r="D124" s="3">
         <v>0.7001849338342101</v>
@@ -9618,7 +9618,7 @@
         <v>-29.88681694059249</v>
       </c>
       <c r="H124">
-        <v>95.39821916139468</v>
+        <v>394.8659066068382</v>
       </c>
       <c r="I124" s="2">
         <v>2.127988835367836</v>
@@ -9669,7 +9669,7 @@
         <v>-88.57206446197429</v>
       </c>
       <c r="C125">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="D125" s="3">
         <v>0.840259544010158</v>
@@ -9688,7 +9688,7 @@
         <v>-29.142888354098826</v>
       </c>
       <c r="H125">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="I125" s="2">
         <v>2.553745585975506</v>
@@ -9739,7 +9739,7 @@
         <v>-90.68922801370987</v>
       </c>
       <c r="C126">
-        <v>95.39821916139468</v>
+        <v>394.8659066068382</v>
       </c>
       <c r="D126" s="3">
         <v>0.7012829877066394</v>
@@ -9758,7 +9758,7 @@
         <v>-29.839581392495596</v>
       </c>
       <c r="H126">
-        <v>95.39821916139468</v>
+        <v>394.8659066068382</v>
       </c>
       <c r="I126" s="2">
         <v>2.1313574053776</v>
@@ -9809,7 +9809,7 @@
         <v>-88.15960863220425</v>
       </c>
       <c r="C127">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="D127" s="3">
         <v>0.8441907087785133</v>
@@ -9828,7 +9828,7 @@
         <v>-29.007400114058935</v>
       </c>
       <c r="H127">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="I127" s="2">
         <v>2.565673662728092</v>
@@ -9879,7 +9879,7 @@
         <v>-90.65860152566356</v>
       </c>
       <c r="C128">
-        <v>95.39821916139468</v>
+        <v>394.8659066068382</v>
       </c>
       <c r="D128" s="3">
         <v>0.701519896667054</v>
@@ -9898,7 +9898,7 @@
         <v>-29.829711182426287</v>
       </c>
       <c r="H128">
-        <v>95.39821916139468</v>
+        <v>394.8659066068382</v>
       </c>
       <c r="I128" s="2">
         <v>2.132062640007436</v>
@@ -9949,7 +9949,7 @@
         <v>-90.09982110235616</v>
       </c>
       <c r="C129">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="D129" s="3">
         <v>0.8260118786729825</v>
@@ -9968,7 +9968,7 @@
         <v>-29.64581693302714</v>
       </c>
       <c r="H129">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="I129" s="2">
         <v>2.5104223865709963</v>
@@ -10019,7 +10019,7 @@
         <v>-92.7554930184054</v>
       </c>
       <c r="C130">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="D130" s="3">
         <v>0.8023624270110779</v>
@@ -10038,7 +10038,7 @@
         <v>-30.519560889416937</v>
       </c>
       <c r="H130">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="I130" s="2">
         <v>2.4385515494970376</v>
@@ -10089,7 +10089,7 @@
         <v>-82.49919236890014</v>
       </c>
       <c r="C131">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="D131" s="3">
         <v>0.9021121341899635</v>
@@ -10108,7 +10108,7 @@
         <v>-27.144811699627247</v>
       </c>
       <c r="H131">
-        <v>111.63528374528528</v>
+        <v>491.79</v>
       </c>
       <c r="I131" s="2">
         <v>2.741721818533699</v>

--- a/calculation_python/outputs/Results_final.xlsx
+++ b/calculation_python/outputs/Results_final.xlsx
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C21">
         <v>1.0</v>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C22">
         <v>1.0</v>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C23">
         <v>1.0</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C24">
         <v>1.0</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C25">
         <v>1.0</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C26">
         <v>1.0</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C27">
         <v>1.0</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C28">
         <v>1.0</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C29">
         <v>1.0</v>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>3.9</v>
+        <v>5.0</v>
       </c>
       <c r="C30">
         <v>1.0</v>
@@ -8550,8 +8550,8 @@
       <c r="F108">
         <v>5.35561134754498</v>
       </c>
-      <c r="G108" s="3">
-        <v>0.954746491348524</v>
+      <c r="G108" s="2">
+        <v>1.6918081722183154</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>5.355683461852774</v>
       </c>
       <c r="O108" s="3">
-        <v>0.30293989921114783</v>
+        <v>0.7759254747871631</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8608,8 +8608,8 @@
       <c r="F109">
         <v>5.086242729498088</v>
       </c>
-      <c r="G109" s="3">
-        <v>0.7396054934381018</v>
+      <c r="G109" s="2">
+        <v>1.2865004950467787</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>5.086304365692135</v>
       </c>
       <c r="O109" s="3">
-        <v>0.2988231730810083</v>
+        <v>0.7520034525039069</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8666,8 +8666,8 @@
       <c r="F110">
         <v>5.067556263084414</v>
       </c>
-      <c r="G110" s="3">
-        <v>0.7231069008395578</v>
+      <c r="G110" s="2">
+        <v>1.256547807079836</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>5.0675142954329315</v>
       </c>
       <c r="O110" s="3">
-        <v>0.2965716531538743</v>
+        <v>0.74542030482537</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -8724,8 +8724,8 @@
       <c r="F111">
         <v>5.069750289424221</v>
       </c>
-      <c r="G111" s="3">
-        <v>0.724943454801876</v>
+      <c r="G111" s="2">
+        <v>1.259952124283611</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>5.069734917815798</v>
       </c>
       <c r="O111" s="3">
-        <v>0.2965668124529481</v>
+        <v>0.7455659573290865</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -8782,8 +8782,8 @@
       <c r="F112">
         <v>5.073432138619901</v>
       </c>
-      <c r="G112" s="3">
-        <v>0.7281005189306851</v>
+      <c r="G112" s="2">
+        <v>1.2657497816126626</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>5.0734268248977825</v>
       </c>
       <c r="O112" s="3">
-        <v>0.29676045643087523</v>
+        <v>0.7462792141100518</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -8840,8 +8840,8 @@
       <c r="F113">
         <v>5.074499368125494</v>
       </c>
-      <c r="G113" s="3">
-        <v>0.7290136819254193</v>
+      <c r="G113" s="2">
+        <v>1.2674278659308384</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>5.074491585023982</v>
       </c>
       <c r="O113" s="3">
-        <v>0.2968129074360182</v>
+        <v>0.7464765711885645</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -8898,8 +8898,8 @@
       <c r="F114">
         <v>5.067904236433945</v>
       </c>
-      <c r="G114" s="3">
-        <v>0.7233577205633106</v>
+      <c r="G114" s="2">
+        <v>1.25704144126647</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>5.067884448642169</v>
       </c>
       <c r="O114" s="3">
-        <v>0.29646531242709123</v>
+        <v>0.7451962032437106</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -8956,8 +8956,8 @@
       <c r="F115">
         <v>5.030467942795777</v>
       </c>
-      <c r="G115" s="3">
-        <v>0.690494278690968</v>
+      <c r="G115" s="2">
+        <v>1.197221576258451</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>5.030461109846401</v>
       </c>
       <c r="O115" s="3">
-        <v>0.2930158647220954</v>
+        <v>0.734380581112165</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -9014,8 +9014,8 @@
       <c r="F116">
         <v>5.014093002699774</v>
       </c>
-      <c r="G116" s="3">
-        <v>0.6761600027495929</v>
+      <c r="G116" s="2">
+        <v>1.1710933582513217</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>5.014092163483752</v>
       </c>
       <c r="O116" s="3">
-        <v>0.2919136225817766</v>
+        <v>0.7305382915071382</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -9072,8 +9072,8 @@
       <c r="F117">
         <v>5.291860976324859</v>
       </c>
-      <c r="G117" s="3">
-        <v>0.9043202222456332</v>
+      <c r="G117" s="2">
+        <v>1.596612127004916</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>5.291858776644743</v>
       </c>
       <c r="O117" s="3">
-        <v>0.29951196653489914</v>
+        <v>0.7649650719350407</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -9526,13 +9526,13 @@
         </is>
       </c>
       <c r="B123">
-        <v>-81.344481801271</v>
+        <v>-81.30330086939975</v>
       </c>
       <c r="C123">
         <v>394.8659066068382</v>
       </c>
       <c r="D123" s="3">
-        <v>0.7818454474839299</v>
+        <v>0.7009924939751038</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -9545,13 +9545,13 @@
         </is>
       </c>
       <c r="G123">
-        <v>-26.76457855379006</v>
+        <v>-26.751180933179835</v>
       </c>
       <c r="H123">
         <v>394.8659066068382</v>
       </c>
       <c r="I123" s="2">
-        <v>2.3762306828947644</v>
+        <v>2.130485520890018</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -9596,13 +9596,13 @@
         </is>
       </c>
       <c r="B124">
-        <v>-90.83144995136678</v>
+        <v>-91.11207876641697</v>
       </c>
       <c r="C124">
         <v>394.8659066068382</v>
       </c>
       <c r="D124" s="3">
-        <v>0.7001849338342101</v>
+        <v>0.6255263233644476</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         </is>
       </c>
       <c r="G124">
-        <v>-29.88681694059249</v>
+        <v>-29.97912608240202</v>
       </c>
       <c r="H124">
         <v>394.8659066068382</v>
       </c>
       <c r="I124" s="2">
-        <v>2.127988835367836</v>
+        <v>1.901089561056421</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="B125">
-        <v>-88.57206446197429</v>
+        <v>-89.41639958378438</v>
       </c>
       <c r="C125">
         <v>491.79</v>
       </c>
       <c r="D125" s="3">
-        <v>0.840259544010158</v>
+        <v>0.7519648635731233</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -9685,13 +9685,13 @@
         </is>
       </c>
       <c r="G125">
-        <v>-29.142888354098826</v>
+        <v>-29.42069443942428</v>
       </c>
       <c r="H125">
         <v>491.79</v>
       </c>
       <c r="I125" s="2">
-        <v>2.553745585975506</v>
+        <v>2.2853978125043892</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="B126">
-        <v>-90.68922801370987</v>
+        <v>-91.09105015140936</v>
       </c>
       <c r="C126">
         <v>394.8659066068382</v>
       </c>
       <c r="D126" s="3">
-        <v>0.7012829877066394</v>
+        <v>0.6256707278060397</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -9755,13 +9755,13 @@
         </is>
       </c>
       <c r="G126">
-        <v>-29.839581392495596</v>
+        <v>-29.97175242052103</v>
       </c>
       <c r="H126">
         <v>394.8659066068382</v>
       </c>
       <c r="I126" s="2">
-        <v>2.1313574053776</v>
+        <v>1.9015572678301866</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="B127">
-        <v>-88.15960863220425</v>
+        <v>-88.97451713368869</v>
       </c>
       <c r="C127">
         <v>491.79</v>
       </c>
       <c r="D127" s="3">
-        <v>0.8441907087785133</v>
+        <v>0.7556994168700216</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -9825,13 +9825,13 @@
         </is>
       </c>
       <c r="G127">
-        <v>-29.007400114058935</v>
+        <v>-29.27549671323102</v>
       </c>
       <c r="H127">
         <v>491.79</v>
       </c>
       <c r="I127" s="2">
-        <v>2.565673662728092</v>
+        <v>2.296732703559294</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -9876,13 +9876,13 @@
         </is>
       </c>
       <c r="B128">
-        <v>-90.65860152566356</v>
+        <v>-91.0732120172231</v>
       </c>
       <c r="C128">
         <v>394.8659066068382</v>
       </c>
       <c r="D128" s="3">
-        <v>0.701519896667054</v>
+        <v>0.6257932753494042</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="G128">
-        <v>-29.829711182426287</v>
+        <v>-29.966124443735396</v>
       </c>
       <c r="H128">
         <v>394.8659066068382</v>
       </c>
       <c r="I128" s="2">
-        <v>2.132062640007436</v>
+        <v>1.9019144017725487</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -9946,13 +9946,13 @@
         </is>
       </c>
       <c r="B129">
-        <v>-90.09982110235616</v>
+        <v>-91.0723926717339</v>
       </c>
       <c r="C129">
         <v>491.79</v>
       </c>
       <c r="D129" s="3">
-        <v>0.8260118786729825</v>
+        <v>0.7382916901785642</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -9965,13 +9965,13 @@
         </is>
       </c>
       <c r="G129">
-        <v>-29.64581693302714</v>
+        <v>-29.965846684826094</v>
       </c>
       <c r="H129">
         <v>491.79</v>
       </c>
       <c r="I129" s="2">
-        <v>2.5104223865709963</v>
+        <v>2.2438208211306048</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -10016,13 +10016,13 @@
         </is>
       </c>
       <c r="B130">
-        <v>-92.7554930184054</v>
+        <v>-93.82351583576055</v>
       </c>
       <c r="C130">
         <v>491.79</v>
       </c>
       <c r="D130" s="3">
-        <v>0.8023624270110779</v>
+        <v>0.7166432649136854</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="G130">
-        <v>-30.519560889416937</v>
+        <v>-30.871001928294593</v>
       </c>
       <c r="H130">
         <v>491.79</v>
       </c>
       <c r="I130" s="2">
-        <v>2.4385515494970376</v>
+        <v>2.1780307250926576</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="B131">
-        <v>-82.49919236890014</v>
+        <v>-83.33196914716758</v>
       </c>
       <c r="C131">
         <v>491.79</v>
       </c>
       <c r="D131" s="3">
-        <v>0.9021121341899635</v>
+        <v>0.8068690972065633</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -10105,13 +10105,13 @@
         </is>
       </c>
       <c r="G131">
-        <v>-27.144811699627247</v>
+        <v>-27.418827505024904</v>
       </c>
       <c r="H131">
         <v>491.79</v>
       </c>
       <c r="I131" s="2">
-        <v>2.741721818533699</v>
+        <v>2.4522562353148745</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -10484,13 +10484,13 @@
         </is>
       </c>
       <c r="B136">
-        <v>56025.30968634687</v>
+        <v>60656.8414917639</v>
       </c>
       <c r="C136">
-        <v>7.280734326468776</v>
+        <v>6.892256831996683</v>
       </c>
       <c r="D136">
-        <v>82.40926987525523</v>
+        <v>87.05421382652979</v>
       </c>
       <c r="E136">
         <v>57.28440140078415</v>
@@ -10558,13 +10558,13 @@
         </is>
       </c>
       <c r="B137">
-        <v>56025.30968634687</v>
+        <v>60656.8414917639</v>
       </c>
       <c r="C137">
-        <v>7.280734326468776</v>
+        <v>6.892256831996683</v>
       </c>
       <c r="D137">
-        <v>82.40926987525523</v>
+        <v>87.05421382652979</v>
       </c>
       <c r="E137">
         <v>57.28440140078415</v>
@@ -10632,13 +10632,13 @@
         </is>
       </c>
       <c r="B138">
-        <v>63450.67812688878</v>
+        <v>69653.87557267422</v>
       </c>
       <c r="C138">
-        <v>7.876001504679489</v>
+        <v>7.486141696402191</v>
       </c>
       <c r="D138">
-        <v>76.18078788373934</v>
+        <v>80.14809555212635</v>
       </c>
       <c r="E138">
         <v>51.33001028308949</v>
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="B139">
-        <v>56025.30968634687</v>
+        <v>60656.8414917639</v>
       </c>
       <c r="C139">
-        <v>7.280734326468776</v>
+        <v>6.892256831996683</v>
       </c>
       <c r="D139">
-        <v>82.40926987525523</v>
+        <v>87.05421382652979</v>
       </c>
       <c r="E139">
         <v>57.28440140078415</v>
@@ -10780,13 +10780,13 @@
         </is>
       </c>
       <c r="B140">
-        <v>63450.67812688878</v>
+        <v>69653.87557267422</v>
       </c>
       <c r="C140">
-        <v>7.876001504679489</v>
+        <v>7.486141696402191</v>
       </c>
       <c r="D140">
-        <v>76.18078788373934</v>
+        <v>80.14809555212635</v>
       </c>
       <c r="E140">
         <v>51.33001028308949</v>
@@ -10854,13 +10854,13 @@
         </is>
       </c>
       <c r="B141">
-        <v>56025.30968634687</v>
+        <v>60656.8414917639</v>
       </c>
       <c r="C141">
-        <v>7.280734326468776</v>
+        <v>6.892256831996683</v>
       </c>
       <c r="D141">
-        <v>82.40926987525523</v>
+        <v>87.05421382652979</v>
       </c>
       <c r="E141">
         <v>57.28440140078415</v>
@@ -10928,13 +10928,13 @@
         </is>
       </c>
       <c r="B142">
-        <v>63450.67812688878</v>
+        <v>69653.87557267422</v>
       </c>
       <c r="C142">
-        <v>7.876001504679489</v>
+        <v>7.486141696402191</v>
       </c>
       <c r="D142">
-        <v>76.18078788373934</v>
+        <v>80.14809555212635</v>
       </c>
       <c r="E142">
         <v>51.33001028308949</v>
@@ -11002,13 +11002,13 @@
         </is>
       </c>
       <c r="B143">
-        <v>63450.67812688878</v>
+        <v>69653.87557267422</v>
       </c>
       <c r="C143">
-        <v>7.876001504679489</v>
+        <v>7.486141696402191</v>
       </c>
       <c r="D143">
-        <v>76.18078788373934</v>
+        <v>80.14809555212635</v>
       </c>
       <c r="E143">
         <v>51.33001028308949</v>
@@ -11076,13 +11076,13 @@
         </is>
       </c>
       <c r="B144">
-        <v>63450.67812688878</v>
+        <v>69653.87557267422</v>
       </c>
       <c r="C144">
-        <v>7.876001504679489</v>
+        <v>7.486141696402191</v>
       </c>
       <c r="D144">
-        <v>76.18078788373934</v>
+        <v>80.14809555212635</v>
       </c>
       <c r="E144">
         <v>51.33001028308949</v>
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="B148" s="3">
-        <v>0.2919136225817766</v>
+        <v>0.7305382915071382</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         </is>
       </c>
       <c r="B149" s="3">
-        <v>0.7001849338342101</v>
+        <v>0.6255263233644476</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="B150" s="3">
-        <v>0.2919136225817766</v>
+        <v>0.6255263233644476</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         </is>
       </c>
       <c r="B153">
-        <v>16.397640000000003</v>
+        <v>19.961640000000003</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>

--- a/calculation_python/outputs/Results_final.xlsx
+++ b/calculation_python/outputs/Results_final.xlsx
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <v>4.29928400579033</v>
+        <v>4.301193798345203</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="E46" s="2">
-        <v>1.6862697871052694</v>
+        <v>1.6866418540863786</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <v>3.686171579798637</v>
+        <v>3.6884435402944864</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E47" s="2">
-        <v>1.6667641928461876</v>
+        <v>1.666944271312615</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <v>4.08332406320587</v>
+        <v>4.087221177684532</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E48" s="2">
-        <v>1.6682410393091816</v>
+        <v>1.668801238354483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <v>3.5067978788898375</v>
+        <v>3.50902472089724</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="E49" s="2">
-        <v>1.6812955539610113</v>
+        <v>1.682038230315753</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="B50" s="2">
-        <v>3.56993215646668</v>
+        <v>3.5787936692572915</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="E50" s="2">
-        <v>1.6643242275236252</v>
+        <v>1.664771826019221</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="B51" s="2">
-        <v>3.640336810174955</v>
+        <v>3.6458482906838636</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="E51" s="2">
-        <v>1.6996779074282877</v>
+        <v>1.7008442665353598</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B52" s="2">
-        <v>3.579723127584637</v>
+        <v>3.5850535102744696</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="E52" s="2">
-        <v>1.6860578929967662</v>
+        <v>1.6878088128813222</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="B53" s="2">
-        <v>3.518964839204503</v>
+        <v>3.5144124862500896</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="E53" s="2">
-        <v>1.6629294666134045</v>
+        <v>1.662728037239743</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="B54" s="2">
-        <v>3.563793807521565</v>
+        <v>3.5561105643466604</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="E54" s="2">
-        <v>1.6838934529788665</v>
+        <v>1.6838591053754521</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="B55" s="2">
-        <v>3.533500143380697</v>
+        <v>3.5238223405166313</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="E55" s="2">
-        <v>1.680588063453574</v>
+        <v>1.679848181759231</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="B56" s="2">
-        <v>3.5474759412942825</v>
+        <v>3.545439754214814</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="E56" s="2">
-        <v>1.6630466270863047</v>
+        <v>1.6631099594680236</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="B57" s="2">
-        <v>3.5931769621505127</v>
+        <v>3.601389464987986</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="E57" s="2">
-        <v>1.6887869812268756</v>
+        <v>1.6905206533009578</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="B58" s="2">
-        <v>3.593358738763461</v>
+        <v>3.6017499875404604</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="E58" s="2">
-        <v>1.6883017612008087</v>
+        <v>1.6900645403658348</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="B59" s="2">
-        <v>3.5590688942461997</v>
+        <v>3.557702519826236</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="E59" s="2">
-        <v>1.6631920962570637</v>
+        <v>1.6632604604971726</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="B60" s="2">
-        <v>3.5419534599691103</v>
+        <v>3.5324641602630034</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="E60" s="2">
-        <v>1.6812642933724777</v>
+        <v>1.680566670291719</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="B61" s="2">
-        <v>3.535550066184406</v>
+        <v>3.5268185038247015</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E61" s="2">
-        <v>1.680502341515763</v>
+        <v>1.6799073366104882</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="B62" s="2">
-        <v>3.566434188760588</v>
+        <v>3.5657260704394136</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="E62" s="2">
-        <v>1.6633069314017392</v>
+        <v>1.6633480952664266</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="B63" s="2">
-        <v>3.5979051046426145</v>
+        <v>3.6064671336536427</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="E63" s="2">
-        <v>1.6890392213131393</v>
+        <v>1.6908258584692966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="B64" s="2">
-        <v>3.5818606805968467</v>
+        <v>3.589251349115322</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="E64" s="2">
-        <v>1.6878414293258814</v>
+        <v>1.689074530032031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="B65" s="2">
-        <v>3.5433757355779036</v>
+        <v>3.5477912418576256</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="E65" s="2">
-        <v>1.6631433542346465</v>
+        <v>1.663412003997066</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="B66" s="2">
-        <v>3.5332930842787236</v>
+        <v>3.5285270180689863</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E66" s="2">
-        <v>1.6811413091186935</v>
+        <v>1.6807004975317723</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="B67" s="2">
-        <v>3.51919370210298</v>
+        <v>3.515338309057187</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="E67" s="2">
-        <v>1.6815155211427506</v>
+        <v>1.6812972475356378</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="B68" s="2">
-        <v>3.4330029330079554</v>
+        <v>3.428695913682162</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="E68" s="2">
-        <v>1.6595083075318617</v>
+        <v>1.6593048859127169</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="B69" s="2">
-        <v>3.4791832121890747</v>
+        <v>3.4806321855624103</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E69" s="2">
-        <v>1.6757744918081123</v>
+        <v>1.676310212597096</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="B70" s="2">
-        <v>3.4920520385868734</v>
+        <v>3.4922040211381313</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="E70" s="2">
-        <v>1.6884751907405868</v>
+        <v>1.6884565331625876</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="B71" s="2">
-        <v>3.4216245270973444</v>
+        <v>3.4218748848991707</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="E71" s="2">
-        <v>1.6571079221975582</v>
+        <v>1.657138996173068</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="B72" s="2">
-        <v>3.360162563082981</v>
+        <v>3.3599742690377066</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="E72" s="2">
-        <v>1.6683176085540246</v>
+        <v>1.668248113738772</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="B73" s="2">
-        <v>3.973115723089309</v>
+        <v>3.9733601755204173</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="E73" s="2">
-        <v>1.65939067198762</v>
+        <v>1.6594348650974322</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="B74" s="2">
-        <v>3.5987328900986224</v>
+        <v>3.599040372870471</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="E74" s="2">
-        <v>1.6631653767467445</v>
+        <v>1.6631543428806377</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="B75" s="2">
-        <v>4.253097235221492</v>
+        <v>4.252970286864102</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="E75" s="2">
-        <v>1.683861668073412</v>
+        <v>1.683873439720825</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B76" s="2">
-        <v>4.597817557626789</v>
+        <v>5.155641862782214</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="E76" s="2">
-        <v>14.428008658485965</v>
+        <v>16.22973607704384</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="B77" s="2">
-        <v>5.070931758627595</v>
+        <v>5.681830060164767</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="E77" s="2">
-        <v>15.41056987175477</v>
+        <v>17.267021973370976</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="B78" s="2">
-        <v>4.571841210246496</v>
+        <v>5.123680292171515</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="E78" s="2">
-        <v>13.47777220598669</v>
+        <v>15.060566328026994</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="B79" s="2">
-        <v>4.479968161401939</v>
+        <v>4.999497597655756</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="E79" s="2">
-        <v>13.58885956509205</v>
+        <v>15.14067553414747</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="B80" s="2">
-        <v>4.368414419299544</v>
+        <v>4.824482059845684</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="E80" s="2">
-        <v>13.275176744208713</v>
+        <v>14.6610433515765</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="B81" s="2">
-        <v>4.481590592947278</v>
+        <v>5.0027577864274875</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="E81" s="2">
-        <v>13.647961796693602</v>
+        <v>15.259425993862761</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="B82" s="2">
-        <v>4.847023184485556</v>
+        <v>4.959644723298203</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="E82" s="2">
-        <v>14.718705625858728</v>
+        <v>15.055322020642087</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="B83" s="2">
-        <v>4.7645826677498535</v>
+        <v>4.992410060618923</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="E83" s="2">
-        <v>14.482469873993262</v>
+        <v>15.175082095165552</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="B84" s="2">
-        <v>4.847629464189299</v>
+        <v>4.960587161729972</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="E84" s="2">
-        <v>14.743433315819415</v>
+        <v>15.092338217047025</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="B85" s="2">
-        <v>4.548420862325247</v>
+        <v>5.04043403514291</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="E85" s="2">
-        <v>13.830543429198844</v>
+        <v>15.326694707660463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="B86" s="2">
-        <v>4.572707263513738</v>
+        <v>4.976815501375589</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="E86" s="2">
-        <v>13.897318952603017</v>
+        <v>15.125469043908433</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="B87" s="2">
-        <v>4.547958330095358</v>
+        <v>5.039920146786564</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="E87" s="2">
-        <v>13.814610378963803</v>
+        <v>15.30887531966145</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="B88" s="2">
-        <v>4.8466607026877035</v>
+        <v>4.9613652079741515</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="E88" s="2">
-        <v>14.732358637132545</v>
+        <v>15.078164284063877</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="B89" s="2">
-        <v>4.766398769925745</v>
+        <v>4.999061936104497</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="E89" s="2">
-        <v>14.485622264909336</v>
+        <v>15.192716621206868</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="B90" s="2">
-        <v>4.8464847896417576</v>
+        <v>4.961365737700774</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="E90" s="2">
-        <v>14.726557418301123</v>
+        <v>15.078509225468425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="B91" s="2">
-        <v>4.550629314295015</v>
+        <v>5.0447011658333745</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E91" s="2">
-        <v>13.824595591495015</v>
+        <v>15.32356990986941</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="B92" s="2">
-        <v>4.591839712463337</v>
+        <v>5.001591445607465</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="E92" s="2">
-        <v>13.955340629150125</v>
+        <v>15.200660998924192</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="B93" s="2">
-        <v>4.5510206271481115</v>
+        <v>5.045256018186837</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="E93" s="2">
-        <v>13.837197859696408</v>
+        <v>15.341913598727217</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="B94" s="2">
-        <v>4.909090120016241</v>
+        <v>4.964652748908433</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="E94" s="2">
-        <v>14.945707037397858</v>
+        <v>15.079174688937757</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="B95" s="2">
-        <v>4.870559444642111</v>
+        <v>4.9861599890550306</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="E95" s="2">
-        <v>14.802892600560083</v>
+        <v>15.154250641894917</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="B96" s="2">
-        <v>4.907599533104889</v>
+        <v>4.965279264361973</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="E96" s="2">
-        <v>14.889777520006874</v>
+        <v>15.100411022038951</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="B97" s="2">
-        <v>4.940583515987535</v>
+        <v>4.931794133701363</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="E97" s="2">
-        <v>15.060954398194635</v>
+        <v>15.035008784212707</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="B98" s="2">
-        <v>4.801838477065307</v>
+        <v>4.7849141055644475</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="E98" s="2">
-        <v>14.594163605974519</v>
+        <v>14.542721507637484</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="B99" s="2">
-        <v>4.937850326991068</v>
+        <v>4.9290152363824795</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="E99" s="2">
-        <v>14.962602607253675</v>
+        <v>14.93499130957703</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="B100" s="2">
-        <v>5.234345471464714</v>
+        <v>5.234278255354964</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="E100" s="2">
-        <v>15.396945103895595</v>
+        <v>15.399590811443295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="B101" s="2">
-        <v>5.775465499135704</v>
+        <v>5.775451501429353</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="E101" s="2">
-        <v>17.553146265309923</v>
+        <v>17.553103165876326</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="B102" s="2">
-        <v>5.266107198760468</v>
+        <v>5.265855361256913</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="E102" s="2">
-        <v>16.55820307846021</v>
+        <v>16.554103369707477</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8536,22 +8536,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>-59.273877461751326</v>
+        <v>-59.20624287923199</v>
       </c>
       <c r="C108">
-        <v>18.600114186605</v>
+        <v>18.600112915039333</v>
       </c>
       <c r="D108">
-        <v>30.783566792806003</v>
+        <v>30.77696355183933</v>
       </c>
       <c r="E108">
         <v>5.7844444444444445</v>
       </c>
       <c r="F108">
-        <v>5.270603803022264</v>
+        <v>5.271894605097841</v>
       </c>
       <c r="G108" s="2">
-        <v>2.0580136301720393</v>
+        <v>2.060691368631207</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8564,22 +8564,22 @@
         </is>
       </c>
       <c r="J108">
-        <v>-19.503446261088</v>
+        <v>-19.481197992960332</v>
       </c>
       <c r="K108">
-        <v>6.120550473531</v>
+        <v>6.120553016662667</v>
       </c>
       <c r="L108">
-        <v>121.54631296793634</v>
+        <v>121.52023824055999</v>
       </c>
       <c r="M108">
         <v>5.7844444444444445</v>
       </c>
       <c r="N108">
-        <v>5.270673660165484</v>
+        <v>5.271964764870574</v>
       </c>
       <c r="O108" s="2">
-        <v>1.207865727610513</v>
+        <v>1.208587315789261</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8594,22 +8594,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>-73.04706064860034</v>
+        <v>-72.87734222412134</v>
       </c>
       <c r="C109">
-        <v>18.600113550822</v>
+        <v>18.600112915039002</v>
       </c>
       <c r="D109">
-        <v>30.560599644979003</v>
+        <v>30.547233581543</v>
       </c>
       <c r="E109">
         <v>5.7844444444444445</v>
       </c>
       <c r="F109">
-        <v>5.065863758536351</v>
+        <v>5.067836744747796</v>
       </c>
       <c r="G109" s="2">
-        <v>1.6392614351264068</v>
+        <v>1.6435047812917616</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8622,22 +8622,22 @@
         </is>
       </c>
       <c r="J109">
-        <v>-24.035125096638996</v>
+        <v>-23.979279200236004</v>
       </c>
       <c r="K109">
-        <v>6.12055460612</v>
+        <v>6.120556195577</v>
       </c>
       <c r="L109">
-        <v>120.66644032796233</v>
+        <v>120.61365763346366</v>
       </c>
       <c r="M109">
         <v>5.7844444444444445</v>
       </c>
       <c r="N109">
-        <v>5.0659252644883805</v>
+        <v>5.067898776532083</v>
       </c>
       <c r="O109" s="2">
-        <v>1.1639953247946027</v>
+        <v>1.165479653972875</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8652,22 +8652,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>-73.62060546875</v>
+        <v>-73.70960744222</v>
       </c>
       <c r="C110">
-        <v>18.599923451741333</v>
+        <v>18.59992535909</v>
       </c>
       <c r="D110">
-        <v>30.633467356364</v>
+        <v>30.623664855957</v>
       </c>
       <c r="E110">
         <v>5.7844444444444445</v>
       </c>
       <c r="F110">
-        <v>5.059266070239923</v>
+        <v>5.058254389088974</v>
       </c>
       <c r="G110" s="2">
-        <v>1.6248724452802714</v>
+        <v>1.6228198205899151</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8680,22 +8680,22 @@
         </is>
       </c>
       <c r="J110">
-        <v>-24.223551432291668</v>
+        <v>-24.252825419108</v>
       </c>
       <c r="K110">
-        <v>6.1196589469910005</v>
+        <v>6.119661966959667</v>
       </c>
       <c r="L110">
-        <v>120.95192464192701</v>
+        <v>120.91321818033866</v>
       </c>
       <c r="M110">
         <v>5.7844444444444445</v>
       </c>
       <c r="N110">
-        <v>5.0592229055366555</v>
+        <v>5.058211984117502</v>
       </c>
       <c r="O110" s="2">
-        <v>1.1573972211929222</v>
+        <v>1.157621370953317</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -8710,22 +8710,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>-73.478520711263</v>
+        <v>-73.52435302734366</v>
       </c>
       <c r="C111">
-        <v>18.599951426188</v>
+        <v>18.599953969319667</v>
       </c>
       <c r="D111">
-        <v>30.637214024861667</v>
+        <v>30.630510965983333</v>
       </c>
       <c r="E111">
         <v>5.7844444444444445</v>
       </c>
       <c r="F111">
-        <v>5.060888464710538</v>
+        <v>5.060364851750048</v>
       </c>
       <c r="G111" s="2">
-        <v>1.6282497826962028</v>
+        <v>1.6272001490397003</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8738,22 +8738,22 @@
         </is>
       </c>
       <c r="J111">
-        <v>-24.176481882731334</v>
+        <v>-24.191566467285</v>
       </c>
       <c r="K111">
-        <v>6.1197859446209995</v>
+        <v>6.119787534077999</v>
       </c>
       <c r="L111">
-        <v>120.96693929036466</v>
+        <v>120.94047292073567</v>
       </c>
       <c r="M111">
         <v>5.7844444444444445</v>
       </c>
       <c r="N111">
-        <v>5.060872450539252</v>
+        <v>5.060348798839903</v>
       </c>
       <c r="O111" s="2">
-        <v>1.1577445611851498</v>
+        <v>1.1579578772972323</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -8768,22 +8768,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>-73.25218709309866</v>
+        <v>-73.28684488932299</v>
       </c>
       <c r="C112">
         <v>18.59997113545733</v>
       </c>
       <c r="D112">
-        <v>30.636516571044996</v>
+        <v>30.629402796427335</v>
       </c>
       <c r="E112">
         <v>5.7844444444444445</v>
       </c>
       <c r="F112">
-        <v>5.063486892840756</v>
+        <v>5.063087926043667</v>
       </c>
       <c r="G112" s="2">
-        <v>1.6337088101377926</v>
+        <v>1.6329250400736652</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8796,22 +8796,22 @@
         </is>
       </c>
       <c r="J112">
-        <v>-24.102127075195334</v>
+        <v>-24.113525390625</v>
       </c>
       <c r="K112">
-        <v>6.1198933919269995</v>
+        <v>6.119892120361333</v>
       </c>
       <c r="L112">
-        <v>120.964111328125</v>
+        <v>120.936030069987</v>
       </c>
       <c r="M112">
         <v>5.7844444444444445</v>
       </c>
       <c r="N112">
-        <v>5.063480696865506</v>
+        <v>5.063081737824568</v>
       </c>
       <c r="O112" s="2">
-        <v>1.1586911757959784</v>
+        <v>1.158973893804956</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -8826,22 +8826,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>-73.18968200683634</v>
+        <v>-73.20691172281933</v>
       </c>
       <c r="C113">
-        <v>18.599982579549</v>
+        <v>18.599981307983334</v>
       </c>
       <c r="D113">
-        <v>30.636320749918998</v>
+        <v>30.62872187296567</v>
       </c>
       <c r="E113">
         <v>5.7844444444444445</v>
       </c>
       <c r="F113">
-        <v>5.064208060838437</v>
+        <v>5.064009210726708</v>
       </c>
       <c r="G113" s="2">
-        <v>1.6352229566556165</v>
+        <v>1.6348632070905662</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8854,22 +8854,22 @@
         </is>
       </c>
       <c r="J113">
-        <v>-24.081757227579665</v>
+        <v>-24.087431589762332</v>
       </c>
       <c r="K113">
-        <v>6.119938532511333</v>
+        <v>6.119934399922667</v>
       </c>
       <c r="L113">
-        <v>120.96351114908866</v>
+        <v>120.93350982666033</v>
       </c>
       <c r="M113">
         <v>5.7844444444444445</v>
       </c>
       <c r="N113">
-        <v>5.064200687801599</v>
+        <v>5.064001144124351</v>
       </c>
       <c r="O113" s="2">
-        <v>1.1589482626879486</v>
+        <v>1.1593295940538657</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -8884,22 +8884,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>-73.65332794189467</v>
+        <v>-73.57988484700533</v>
       </c>
       <c r="C114">
-        <v>18.599974314371664</v>
+        <v>18.599974314371668</v>
       </c>
       <c r="D114">
-        <v>30.637740453084334</v>
+        <v>30.63168334960934</v>
       </c>
       <c r="E114">
         <v>5.7844444444444445</v>
       </c>
       <c r="F114">
-        <v>5.058896043073907</v>
+        <v>5.0597322237473294</v>
       </c>
       <c r="G114" s="2">
-        <v>1.6240590489408646</v>
+        <v>1.6258608926548508</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -8912,22 +8912,22 @@
         </is>
       </c>
       <c r="J114">
-        <v>-24.234440485636338</v>
+        <v>-24.21028010050467</v>
       </c>
       <c r="K114">
-        <v>6.119883696238333</v>
+        <v>6.119886398315334</v>
       </c>
       <c r="L114">
-        <v>120.96950785319001</v>
+        <v>120.94559733072934</v>
       </c>
       <c r="M114">
         <v>5.7844444444444445</v>
       </c>
       <c r="N114">
-        <v>5.058877145845331</v>
+        <v>5.059713502597948</v>
       </c>
       <c r="O114" s="2">
-        <v>1.157003548046308</v>
+        <v>1.157654570941569</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -8942,22 +8942,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>-76.179796854655</v>
+        <v>-76.26045481363934</v>
       </c>
       <c r="C115">
-        <v>18.599989573160663</v>
+        <v>18.599990208943666</v>
       </c>
       <c r="D115">
-        <v>30.716664632161333</v>
+        <v>30.715451558431003</v>
       </c>
       <c r="E115">
         <v>5.7844444444444445</v>
       </c>
       <c r="F115">
-        <v>5.031269783148089</v>
+        <v>5.030422762887383</v>
       </c>
       <c r="G115" s="2">
-        <v>1.5653139850563038</v>
+        <v>1.5635343359839362</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -8970,22 +8970,22 @@
         </is>
       </c>
       <c r="J115">
-        <v>-25.065788904825997</v>
+        <v>-25.092327117920004</v>
       </c>
       <c r="K115">
-        <v>6.119986693064001</v>
+        <v>6.119988282521667</v>
       </c>
       <c r="L115">
-        <v>121.28137461344433</v>
+        <v>121.27658589680968</v>
       </c>
       <c r="M115">
         <v>5.7844444444444445</v>
       </c>
       <c r="N115">
-        <v>5.03126279194466</v>
+        <v>5.030415995174932</v>
       </c>
       <c r="O115" s="2">
-        <v>1.1424376887671566</v>
+        <v>1.1421940410406406</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -9000,22 +9000,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>-77.95729319254568</v>
+        <v>-77.95453898112001</v>
       </c>
       <c r="C116">
-        <v>18.599996566772333</v>
+        <v>18.599998474121335</v>
       </c>
       <c r="D116">
-        <v>30.723674774169996</v>
+        <v>30.72404607137033</v>
       </c>
       <c r="E116">
         <v>5.7844444444444445</v>
       </c>
       <c r="F116">
-        <v>5.013072587879022</v>
+        <v>5.013100122942445</v>
       </c>
       <c r="G116" s="2">
-        <v>1.5267878416099367</v>
+        <v>1.5268435644098386</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9028,22 +9028,22 @@
         </is>
       </c>
       <c r="J116">
-        <v>-25.650537490845</v>
+        <v>-25.649628321330002</v>
       </c>
       <c r="K116">
-        <v>6.120011011759333</v>
+        <v>6.120010058085</v>
       </c>
       <c r="L116">
-        <v>121.309117635091</v>
+        <v>121.31058502197233</v>
       </c>
       <c r="M116">
         <v>5.7844444444444445</v>
       </c>
       <c r="N116">
-        <v>5.013071909528566</v>
+        <v>5.0130993329234075</v>
       </c>
       <c r="O116" s="2">
-        <v>1.1351656943373805</v>
+        <v>1.1351551085217864</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -9058,22 +9058,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>-61.53027089436866</v>
+        <v>-61.526178995768326</v>
       </c>
       <c r="C117">
-        <v>18.599970499674335</v>
+        <v>18.59997113545733</v>
       </c>
       <c r="D117">
-        <v>30.864727656046668</v>
+        <v>30.864473978678337</v>
       </c>
       <c r="E117">
         <v>5.7844444444444445</v>
       </c>
       <c r="F117">
-        <v>5.229489675554291</v>
+        <v>5.229560967596806</v>
       </c>
       <c r="G117" s="2">
-        <v>1.9740388262785675</v>
+        <v>1.9741861020171456</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9086,22 +9086,22 @@
         </is>
       </c>
       <c r="J117">
-        <v>-20.245260874430333</v>
+        <v>-20.243912378946998</v>
       </c>
       <c r="K117">
-        <v>6.119926293690667</v>
+        <v>6.119933287302667</v>
       </c>
       <c r="L117">
-        <v>121.86581166585302</v>
+        <v>121.86480458577499</v>
       </c>
       <c r="M117">
         <v>5.7844444444444445</v>
       </c>
       <c r="N117">
-        <v>5.229488161007643</v>
+        <v>5.229560754058314</v>
       </c>
       <c r="O117" s="2">
-        <v>1.1930020561701011</v>
+        <v>1.1930356296666178</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -9526,13 +9526,13 @@
         </is>
       </c>
       <c r="B123">
-        <v>-68.22788061746733</v>
+        <v>-66.2182411876153</v>
       </c>
       <c r="C123">
         <v>387.59333725408175</v>
       </c>
       <c r="D123" s="2">
-        <v>1.1103291128444512</v>
+        <v>1.1440261897414763</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -9545,13 +9545,13 @@
         </is>
       </c>
       <c r="G123">
-        <v>-22.448839632476204</v>
+        <v>-21.787659152736435</v>
       </c>
       <c r="H123">
         <v>387.59333725408175</v>
       </c>
       <c r="I123" s="2">
-        <v>3.37457986236652</v>
+        <v>3.4769867486078736</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -9596,13 +9596,13 @@
         </is>
       </c>
       <c r="B124">
-        <v>-74.87117329264078</v>
+        <v>-72.92718797389094</v>
       </c>
       <c r="C124">
         <v>387.59333725408175</v>
       </c>
       <c r="D124" s="2">
-        <v>1.0118100041140368</v>
+        <v>1.0387813415261704</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         </is>
       </c>
       <c r="G124">
-        <v>-24.635270159419008</v>
+        <v>-23.995632429433044</v>
       </c>
       <c r="H124">
         <v>387.59333725408175</v>
       </c>
       <c r="I124" s="2">
-        <v>3.075079009364362</v>
+        <v>3.157049616426365</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="B125">
-        <v>-73.55172044274082</v>
+        <v>-73.1681154413481</v>
       </c>
       <c r="C125">
         <v>491.79</v>
       </c>
       <c r="D125" s="3">
-        <v>0.914159319584704</v>
+        <v>0.918952064142182</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -9685,13 +9685,13 @@
         </is>
       </c>
       <c r="G125">
-        <v>-24.200766835800444</v>
+        <v>-24.074543884354515</v>
       </c>
       <c r="H125">
         <v>491.79</v>
       </c>
       <c r="I125" s="2">
-        <v>2.7783413298604422</v>
+        <v>2.792908187054655</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="B126">
-        <v>-74.42188124928036</v>
+        <v>-72.747284230178</v>
       </c>
       <c r="C126">
         <v>387.59333725408175</v>
       </c>
       <c r="D126" s="2">
-        <v>1.0179183982665336</v>
+        <v>1.0413502436400748</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -9755,13 +9755,13 @@
         </is>
       </c>
       <c r="G126">
-        <v>-24.48712184177191</v>
+        <v>-23.93611706756957</v>
       </c>
       <c r="H126">
         <v>387.59333725408175</v>
       </c>
       <c r="I126" s="2">
-        <v>3.093683391897065</v>
+        <v>3.1648993837805333</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="B127">
-        <v>-73.28694626362604</v>
+        <v>-72.8618375583078</v>
       </c>
       <c r="C127">
         <v>491.79</v>
       </c>
       <c r="D127" s="3">
-        <v>0.9174620330386454</v>
+        <v>0.9228149188580784</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -9825,13 +9825,13 @@
         </is>
       </c>
       <c r="G127">
-        <v>-24.113805847891395</v>
+        <v>-23.973925351032513</v>
       </c>
       <c r="H127">
         <v>491.79</v>
       </c>
       <c r="I127" s="2">
-        <v>2.7883607895972116</v>
+        <v>2.804630019060457</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -9876,13 +9876,13 @@
         </is>
       </c>
       <c r="B128">
-        <v>-74.43191656252255</v>
+        <v>-72.6994006691911</v>
       </c>
       <c r="C128">
         <v>387.59333725408175</v>
       </c>
       <c r="D128" s="2">
-        <v>1.0177811570069588</v>
+        <v>1.0420361304209982</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="G128">
-        <v>-24.490593034077367</v>
+        <v>-23.920534804584495</v>
       </c>
       <c r="H128">
         <v>387.59333725408175</v>
       </c>
       <c r="I128" s="2">
-        <v>3.093244906394875</v>
+        <v>3.1669610556838683</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -9946,13 +9946,13 @@
         </is>
       </c>
       <c r="B129">
-        <v>-74.42767426372612</v>
+        <v>-74.2133416088431</v>
       </c>
       <c r="C129">
         <v>491.79</v>
       </c>
       <c r="D129" s="3">
-        <v>0.9034004001787026</v>
+        <v>0.9060094756090107</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -9965,13 +9965,13 @@
         </is>
       </c>
       <c r="G129">
-        <v>-24.489167658193377</v>
+        <v>-24.418644099885476</v>
       </c>
       <c r="H129">
         <v>491.79</v>
       </c>
       <c r="I129" s="2">
-        <v>2.7456217235592484</v>
+        <v>2.7535513617865317</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -10016,13 +10016,13 @@
         </is>
       </c>
       <c r="B130">
-        <v>-76.16816409445289</v>
+        <v>-76.23322758967643</v>
       </c>
       <c r="C130">
         <v>491.79</v>
       </c>
       <c r="D130" s="3">
-        <v>0.8827571402514224</v>
+        <v>0.8820037251489234</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="G130">
-        <v>-25.06179133715454</v>
+        <v>-25.08319830763531</v>
       </c>
       <c r="H130">
         <v>491.79</v>
       </c>
       <c r="I130" s="2">
-        <v>2.6828884579586627</v>
+        <v>2.6805987772999864</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="B131">
-        <v>-68.91020450336694</v>
+        <v>-68.90772643942142</v>
       </c>
       <c r="C131">
         <v>491.79</v>
       </c>
       <c r="D131" s="3">
-        <v>0.9757334374321159</v>
+        <v>0.9757685268187011</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -10105,13 +10105,13 @@
         </is>
       </c>
       <c r="G131">
-        <v>-22.67360744949399</v>
+        <v>-22.67279015592485</v>
       </c>
       <c r="H131">
         <v>491.79</v>
       </c>
       <c r="I131" s="2">
-        <v>2.965473882530363</v>
+        <v>2.9655807799486764</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="B147" s="2">
-        <v>1.6571079221975582</v>
+        <v>1.657138996173068</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="B148" s="2">
-        <v>1.1351656943373805</v>
+        <v>1.1351551085217864</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         </is>
       </c>
       <c r="B149" s="3">
-        <v>0.8827571402514224</v>
+        <v>0.8820037251489234</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="B150" s="3">
-        <v>0.8827571402514224</v>
+        <v>0.8820037251489234</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>

--- a/calculation_python/outputs/Results_final.xlsx
+++ b/calculation_python/outputs/Results_final.xlsx
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="E57" s="2">
-        <v>1.6905206533009578</v>
+        <v>1.6905206533009576</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>

--- a/calculation_python/outputs/Results_final.xlsx
+++ b/calculation_python/outputs/Results_final.xlsx
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="B32">
-        <v>3.0</v>
+        <v>2.1</v>
       </c>
       <c r="C32">
-        <v>42.0</v>
+        <v>55.0</v>
       </c>
       <c r="D32">
-        <v>9.375</v>
+        <v>11.371794871794872</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="B33">
-        <v>3.0</v>
+        <v>2.1</v>
       </c>
       <c r="C33">
-        <v>42.0</v>
+        <v>55.0</v>
       </c>
       <c r="D33">
-        <v>9.375</v>
+        <v>11.371794871794872</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2814,13 +2814,13 @@
         </is>
       </c>
       <c r="B35">
-        <v>3.0</v>
+        <v>2.1</v>
       </c>
       <c r="C35">
-        <v>42.0</v>
+        <v>55.0</v>
       </c>
       <c r="D35">
-        <v>9.375</v>
+        <v>11.371794871794872</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="B37">
-        <v>3.0</v>
+        <v>2.1</v>
       </c>
       <c r="C37">
-        <v>42.0</v>
+        <v>55.0</v>
       </c>
       <c r="D37">
-        <v>9.375</v>
+        <v>11.371794871794872</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <v>4.301193798345203</v>
+        <v>4.294539485208779</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="E46" s="2">
-        <v>1.6866418540863786</v>
+        <v>1.6875157757509338</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <v>3.6884435402944864</v>
+        <v>3.6730805994301385</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E47" s="2">
-        <v>1.666944271312615</v>
+        <v>1.6670271369762553</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <v>4.087221177684532</v>
+        <v>4.070226023595548</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E48" s="2">
-        <v>1.668801238354483</v>
+        <v>1.6686408621969662</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <v>3.50902472089724</v>
+        <v>3.481713704492909</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="E49" s="2">
-        <v>1.682038230315753</v>
+        <v>1.682659409012414</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="B50" s="2">
-        <v>3.5787936692572915</v>
+        <v>3.5498401609169714</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="E50" s="2">
-        <v>1.664771826019221</v>
+        <v>1.6647747740362473</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="B51" s="2">
-        <v>3.6458482906838636</v>
+        <v>3.615547258111587</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="E51" s="2">
-        <v>1.7008442665353598</v>
+        <v>1.701527513301477</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B52" s="2">
-        <v>3.5850535102744696</v>
+        <v>3.5600560013789138</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="E52" s="2">
-        <v>1.6878088128813222</v>
+        <v>1.6874119836051793</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="B53" s="2">
-        <v>3.5144124862500896</v>
+        <v>3.4938078534445367</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="E53" s="2">
-        <v>1.662728037239743</v>
+        <v>1.6624609946202498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="B54" s="2">
-        <v>3.5561105643466604</v>
+        <v>3.5464433839054657</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="E54" s="2">
-        <v>1.6838591053754521</v>
+        <v>1.6855293650739018</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="B55" s="2">
-        <v>3.5238223405166313</v>
+        <v>3.514717127714317</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="E55" s="2">
-        <v>1.679848181759231</v>
+        <v>1.681147935189644</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="B56" s="2">
-        <v>3.545439754214814</v>
+        <v>3.528771171420777</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="E56" s="2">
-        <v>1.6631099594680236</v>
+        <v>1.6630291587106383</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="B57" s="2">
-        <v>3.601389464987986</v>
+        <v>3.576240524551117</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="E57" s="2">
-        <v>1.6905206533009576</v>
+        <v>1.6897405122820959</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="B58" s="2">
-        <v>3.6017499875404604</v>
+        <v>3.5776794780537804</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="E58" s="2">
-        <v>1.6900645403658348</v>
+        <v>1.6893991188567163</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="B59" s="2">
-        <v>3.557702519826236</v>
+        <v>3.5404254210684223</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="E59" s="2">
-        <v>1.6632604604971726</v>
+        <v>1.6632024378091932</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="B60" s="2">
-        <v>3.5324641602630034</v>
+        <v>3.523021702996304</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="E60" s="2">
-        <v>1.680566670291719</v>
+        <v>1.6817959788422372</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="B61" s="2">
-        <v>3.5268185038247015</v>
+        <v>3.5190275203731756</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E61" s="2">
-        <v>1.6799073366104882</v>
+        <v>1.6813713678724984</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="B62" s="2">
-        <v>3.5657260704394136</v>
+        <v>3.5467756990901034</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="E62" s="2">
-        <v>1.6633480952664266</v>
+        <v>1.663251695154944</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="B63" s="2">
-        <v>3.6064671336536427</v>
+        <v>3.581402668130521</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="E63" s="2">
-        <v>1.6908258584692966</v>
+        <v>1.690045449056631</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="B64" s="2">
-        <v>3.589251349115322</v>
+        <v>3.5665198857137694</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="E64" s="2">
-        <v>1.689074530032031</v>
+        <v>1.6883566372538423</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="B65" s="2">
-        <v>3.5477912418576256</v>
+        <v>3.5328351193910956</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="E65" s="2">
-        <v>1.663412003997066</v>
+        <v>1.6634680426904453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="B66" s="2">
-        <v>3.5285270180689863</v>
+        <v>3.519364335261394</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E66" s="2">
-        <v>1.6807004975317723</v>
+        <v>1.6817633909275413</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="B67" s="2">
-        <v>3.515338309057187</v>
+        <v>3.5155936415104048</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="E67" s="2">
-        <v>1.6812972475356378</v>
+        <v>1.6815367722666439</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="B68" s="2">
-        <v>3.428695913682162</v>
+        <v>3.426995493140162</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="E68" s="2">
-        <v>1.6593048859127169</v>
+        <v>1.659180123358753</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="B69" s="2">
-        <v>3.4806321855624103</v>
+        <v>3.479551564164482</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E69" s="2">
-        <v>1.676310212597096</v>
+        <v>1.6763548332210474</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="B70" s="2">
-        <v>3.4922040211381313</v>
+        <v>3.4930192748248414</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="E70" s="2">
-        <v>1.6884565331625876</v>
+        <v>1.6885501194476966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="B71" s="2">
-        <v>3.4218748848991707</v>
+        <v>3.423815006785263</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="E71" s="2">
-        <v>1.657138996173068</v>
+        <v>1.657175741031117</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="B72" s="2">
-        <v>3.3599742690377066</v>
+        <v>3.359111702685511</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="E72" s="2">
-        <v>1.668248113738772</v>
+        <v>1.6680857389537442</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="B73" s="2">
-        <v>3.9733601755204173</v>
+        <v>3.9737339091955555</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="E73" s="2">
-        <v>1.6594348650974322</v>
+        <v>1.65947628079372</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="B74" s="2">
-        <v>3.599040372870471</v>
+        <v>3.599476716958905</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="E74" s="2">
-        <v>1.6631543428806377</v>
+        <v>1.6631500871577718</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="B75" s="2">
-        <v>4.252970286864102</v>
+        <v>4.2530161533825614</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="E75" s="2">
-        <v>1.683873439720825</v>
+        <v>1.6838837155031787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B76" s="2">
-        <v>5.155641862782214</v>
+        <v>5.233671030157329</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="E76" s="2">
-        <v>16.22973607704384</v>
+        <v>16.49570322843346</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="B77" s="2">
-        <v>5.681830060164767</v>
+        <v>5.7869196584909615</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="E77" s="2">
-        <v>17.267021973370976</v>
+        <v>17.586069643532014</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="B78" s="2">
-        <v>5.123680292171515</v>
+        <v>5.200107458665923</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="E78" s="2">
-        <v>15.060566328026994</v>
+        <v>15.268142620286948</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="B79" s="2">
-        <v>4.999497597655756</v>
+        <v>5.1257002351411485</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="E79" s="2">
-        <v>15.14067553414747</v>
+        <v>15.51560719450454</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="B80" s="2">
-        <v>4.824482059845684</v>
+        <v>4.9270893200272505</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="E80" s="2">
-        <v>14.6610433515765</v>
+        <v>14.972671698033828</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="B81" s="2">
-        <v>5.0027577864274875</v>
+        <v>5.129495179995125</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="E81" s="2">
-        <v>15.259425993862761</v>
+        <v>15.653439291635081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="B82" s="2">
-        <v>4.959644723298203</v>
+        <v>4.984452209156346</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="E82" s="2">
-        <v>15.055322020642087</v>
+        <v>15.118014966194307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="B83" s="2">
-        <v>4.992410060618923</v>
+        <v>5.032613512196029</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="E83" s="2">
-        <v>15.175082095165552</v>
+        <v>15.297291503145384</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="B84" s="2">
-        <v>4.960587161729972</v>
+        <v>4.986156778850298</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="E84" s="2">
-        <v>15.092338217047025</v>
+        <v>15.182809600877297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="B85" s="2">
-        <v>5.04043403514291</v>
+        <v>5.165918136448703</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="E85" s="2">
-        <v>15.326694707660463</v>
+        <v>15.71023989335279</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="B86" s="2">
-        <v>4.976815501375589</v>
+        <v>5.101030712900475</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="E86" s="2">
-        <v>15.125469043908433</v>
+        <v>15.503007655811183</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="B87" s="2">
-        <v>5.039920146786564</v>
+        <v>5.165273269807008</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="E87" s="2">
-        <v>15.30887531966145</v>
+        <v>15.687645560757037</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="B88" s="2">
-        <v>4.9613652079741515</v>
+        <v>4.981449185250068</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="E88" s="2">
-        <v>15.078164284063877</v>
+        <v>15.138962630409768</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="B89" s="2">
-        <v>4.999061936104497</v>
+        <v>5.02728203485955</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="E89" s="2">
-        <v>15.192716621206868</v>
+        <v>15.278506714153767</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="B90" s="2">
-        <v>4.961365737700774</v>
+        <v>4.981475352561514</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="E90" s="2">
-        <v>15.078509225468425</v>
+        <v>15.139891175907504</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="B91" s="2">
-        <v>5.0447011658333745</v>
+        <v>5.16935707939105</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E91" s="2">
-        <v>15.32356990986941</v>
+        <v>15.699231617631261</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="B92" s="2">
-        <v>5.001591445607465</v>
+        <v>5.122614445027513</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="E92" s="2">
-        <v>15.200660998924192</v>
+        <v>15.568501633359912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="B93" s="2">
-        <v>5.045256018186837</v>
+        <v>5.170103630949604</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="E93" s="2">
-        <v>15.341913598727217</v>
+        <v>15.724604615458013</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="B94" s="2">
-        <v>4.964652748908433</v>
+        <v>4.97366834601145</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="E94" s="2">
-        <v>15.079174688937757</v>
+        <v>15.089237191805108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="B95" s="2">
-        <v>4.9861599890550306</v>
+        <v>4.999293203769039</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="E95" s="2">
-        <v>15.154250641894917</v>
+        <v>15.194179631312323</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="B96" s="2">
-        <v>4.965279264361973</v>
+        <v>4.975335181877686</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="E96" s="2">
-        <v>15.100411022038951</v>
+        <v>15.148426055178707</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="B97" s="2">
-        <v>4.931794133701363</v>
+        <v>4.9307134860945006</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="E97" s="2">
-        <v>15.035008784212707</v>
+        <v>15.028317925993223</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="B98" s="2">
-        <v>4.7849141055644475</v>
+        <v>4.78489784595573</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="E98" s="2">
-        <v>14.542721507637484</v>
+        <v>14.542670305074076</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="B99" s="2">
-        <v>4.9290152363824795</v>
+        <v>4.928137542623586</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="E99" s="2">
-        <v>14.93499130957703</v>
+        <v>14.935681370128268</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="B100" s="2">
-        <v>5.234278255354964</v>
+        <v>5.23451175031139</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="E100" s="2">
-        <v>15.399590811443295</v>
+        <v>15.404025749596126</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="B101" s="2">
-        <v>5.775451501429353</v>
+        <v>5.776155777899696</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="E101" s="2">
-        <v>17.553103165876326</v>
+        <v>17.555245132299873</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="B102" s="2">
-        <v>5.265855361256913</v>
+        <v>5.2658482003530445</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="E102" s="2">
-        <v>16.554103369707477</v>
+        <v>16.549725707429914</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8536,22 +8536,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>-59.20624287923199</v>
+        <v>-59.59139251708999</v>
       </c>
       <c r="C108">
-        <v>18.600112915039333</v>
+        <v>18.600114186605</v>
       </c>
       <c r="D108">
-        <v>30.77696355183933</v>
+        <v>30.770037333170666</v>
       </c>
       <c r="E108">
         <v>5.7844444444444445</v>
       </c>
       <c r="F108">
-        <v>5.271894605097841</v>
+        <v>5.26459119230698</v>
       </c>
       <c r="G108" s="2">
-        <v>2.060691368631207</v>
+        <v>2.046065081166741</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8564,22 +8564,22 @@
         </is>
       </c>
       <c r="J108">
-        <v>-19.481197992960332</v>
+        <v>-19.607909838358665</v>
       </c>
       <c r="K108">
-        <v>6.120553016662667</v>
+        <v>6.120551109314</v>
       </c>
       <c r="L108">
-        <v>121.52023824055999</v>
+        <v>121.49289194742833</v>
       </c>
       <c r="M108">
         <v>5.7844444444444445</v>
       </c>
       <c r="N108">
-        <v>5.271964764870574</v>
+        <v>5.2646612879452235</v>
       </c>
       <c r="O108" s="2">
-        <v>1.208587315789261</v>
+        <v>1.2073604371471607</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8594,22 +8594,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>-72.87734222412134</v>
+        <v>-73.85754903157567</v>
       </c>
       <c r="C109">
         <v>18.600112915039002</v>
       </c>
       <c r="D109">
-        <v>30.547233581543</v>
+        <v>30.533096949259328</v>
       </c>
       <c r="E109">
         <v>5.7844444444444445</v>
       </c>
       <c r="F109">
-        <v>5.067836744747796</v>
+        <v>5.056587302123366</v>
       </c>
       <c r="G109" s="2">
-        <v>1.6435047812917616</v>
+        <v>1.6199720620847442</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8622,22 +8622,22 @@
         </is>
       </c>
       <c r="J109">
-        <v>-23.979279200236004</v>
+        <v>-24.301781336466668</v>
       </c>
       <c r="K109">
-        <v>6.120556195577</v>
+        <v>6.120554288228666</v>
       </c>
       <c r="L109">
-        <v>120.61365763346366</v>
+        <v>120.557861328125</v>
       </c>
       <c r="M109">
         <v>5.7844444444444445</v>
       </c>
       <c r="N109">
-        <v>5.067898776532083</v>
+        <v>5.056648711509736</v>
       </c>
       <c r="O109" s="2">
-        <v>1.165479653972875</v>
+        <v>1.162364311401517</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8652,22 +8652,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>-73.70960744222</v>
+        <v>-74.34720357259134</v>
       </c>
       <c r="C110">
-        <v>18.59992535909</v>
+        <v>18.599923451741667</v>
       </c>
       <c r="D110">
-        <v>30.623664855957</v>
+        <v>30.613504409790004</v>
       </c>
       <c r="E110">
         <v>5.7844444444444445</v>
       </c>
       <c r="F110">
-        <v>5.058254389088974</v>
+        <v>5.051088601320718</v>
       </c>
       <c r="G110" s="2">
-        <v>1.6228198205899151</v>
+        <v>1.6078257237738784</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8680,22 +8680,22 @@
         </is>
       </c>
       <c r="J110">
-        <v>-24.252825419108</v>
+        <v>-24.462598164876667</v>
       </c>
       <c r="K110">
-        <v>6.119661966959667</v>
+        <v>6.1196630795796665</v>
       </c>
       <c r="L110">
-        <v>120.91321818033866</v>
+        <v>120.87309773763033</v>
       </c>
       <c r="M110">
         <v>5.7844444444444445</v>
       </c>
       <c r="N110">
-        <v>5.058211984117502</v>
+        <v>5.051047483500603</v>
       </c>
       <c r="O110" s="2">
-        <v>1.157621370953317</v>
+        <v>1.1556788098364836</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -8710,22 +8710,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>-73.52435302734366</v>
+        <v>-74.10671742757168</v>
       </c>
       <c r="C111">
-        <v>18.599953969319667</v>
+        <v>18.599953333537</v>
       </c>
       <c r="D111">
-        <v>30.630510965983333</v>
+        <v>30.624097188313666</v>
       </c>
       <c r="E111">
         <v>5.7844444444444445</v>
       </c>
       <c r="F111">
-        <v>5.060364851750048</v>
+        <v>5.053775805161672</v>
       </c>
       <c r="G111" s="2">
-        <v>1.6272001490397003</v>
+        <v>1.613399088217573</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8738,22 +8738,22 @@
         </is>
       </c>
       <c r="J111">
-        <v>-24.191566467285</v>
+        <v>-24.383182525635</v>
       </c>
       <c r="K111">
-        <v>6.119787534077999</v>
+        <v>6.119788010915</v>
       </c>
       <c r="L111">
-        <v>120.94047292073567</v>
+        <v>120.91515858968067</v>
       </c>
       <c r="M111">
         <v>5.7844444444444445</v>
       </c>
       <c r="N111">
-        <v>5.060348798839903</v>
+        <v>5.053759948278408</v>
       </c>
       <c r="O111" s="2">
-        <v>1.1579578772972323</v>
+        <v>1.1560130842732599</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -8768,22 +8768,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>-73.28684488932299</v>
+        <v>-73.86626180013033</v>
       </c>
       <c r="C112">
-        <v>18.59997113545733</v>
+        <v>18.599972407023</v>
       </c>
       <c r="D112">
-        <v>30.629402796427335</v>
+        <v>30.622621536255</v>
       </c>
       <c r="E112">
         <v>5.7844444444444445</v>
       </c>
       <c r="F112">
-        <v>5.063087926043667</v>
+        <v>5.0564825656140435</v>
       </c>
       <c r="G112" s="2">
-        <v>1.6329250400736652</v>
+        <v>1.6190998471408604</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8796,22 +8796,22 @@
         </is>
       </c>
       <c r="J112">
-        <v>-24.113525390625</v>
+        <v>-24.304182688395333</v>
       </c>
       <c r="K112">
-        <v>6.119892120361333</v>
+        <v>6.119893391927</v>
       </c>
       <c r="L112">
-        <v>120.936030069987</v>
+        <v>120.90924835205065</v>
       </c>
       <c r="M112">
         <v>5.7844444444444445</v>
       </c>
       <c r="N112">
-        <v>5.063081737824568</v>
+        <v>5.05647614256255</v>
       </c>
       <c r="O112" s="2">
-        <v>1.158973893804956</v>
+        <v>1.1570592508150843</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -8826,22 +8826,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>-73.20691172281933</v>
+        <v>-73.79817199707</v>
       </c>
       <c r="C113">
-        <v>18.599981307983334</v>
+        <v>18.599981307983665</v>
       </c>
       <c r="D113">
-        <v>30.62872187296567</v>
+        <v>30.621356964111335</v>
       </c>
       <c r="E113">
         <v>5.7844444444444445</v>
       </c>
       <c r="F113">
-        <v>5.064009210726708</v>
+        <v>5.057252930087406</v>
       </c>
       <c r="G113" s="2">
-        <v>1.6348632070905662</v>
+        <v>1.6207277957734516</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8854,22 +8854,22 @@
         </is>
       </c>
       <c r="J113">
-        <v>-24.087431589762332</v>
+        <v>-24.281985600789668</v>
       </c>
       <c r="K113">
-        <v>6.119934399922667</v>
+        <v>6.119934717814333</v>
       </c>
       <c r="L113">
-        <v>120.93350982666033</v>
+        <v>120.90442657470733</v>
       </c>
       <c r="M113">
         <v>5.7844444444444445</v>
       </c>
       <c r="N113">
-        <v>5.064001144124351</v>
+        <v>5.057244637132175</v>
       </c>
       <c r="O113" s="2">
-        <v>1.1593295940538657</v>
+        <v>1.1574009172606454</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -8884,22 +8884,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>-73.57988484700533</v>
+        <v>-74.11598459879568</v>
       </c>
       <c r="C114">
-        <v>18.599974314371668</v>
+        <v>18.599973678589</v>
       </c>
       <c r="D114">
-        <v>30.63168334960934</v>
+        <v>30.625796000163003</v>
       </c>
       <c r="E114">
         <v>5.7844444444444445</v>
       </c>
       <c r="F114">
-        <v>5.0597322237473294</v>
+        <v>5.053672837177586</v>
       </c>
       <c r="G114" s="2">
-        <v>1.6258608926548508</v>
+        <v>1.6131683742099063</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -8912,22 +8912,22 @@
         </is>
       </c>
       <c r="J114">
-        <v>-24.21028010050467</v>
+        <v>-24.386686325073327</v>
       </c>
       <c r="K114">
-        <v>6.119886398315334</v>
+        <v>6.119884808858</v>
       </c>
       <c r="L114">
-        <v>120.94559733072934</v>
+        <v>120.92235056559267</v>
       </c>
       <c r="M114">
         <v>5.7844444444444445</v>
       </c>
       <c r="N114">
-        <v>5.059713502597948</v>
+        <v>5.053653726908456</v>
       </c>
       <c r="O114" s="2">
-        <v>1.157654570941569</v>
+        <v>1.1558639826643111</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -8942,22 +8942,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>-76.26045481363934</v>
+        <v>-76.29179382324233</v>
       </c>
       <c r="C115">
-        <v>18.599990208943666</v>
+        <v>18.599988937377997</v>
       </c>
       <c r="D115">
-        <v>30.715451558431003</v>
+        <v>30.714287439981998</v>
       </c>
       <c r="E115">
         <v>5.7844444444444445</v>
       </c>
       <c r="F115">
-        <v>5.030422762887383</v>
+        <v>5.030094154526985</v>
       </c>
       <c r="G115" s="2">
-        <v>1.5635343359839362</v>
+        <v>1.5628487411623977</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -8970,22 +8970,22 @@
         </is>
       </c>
       <c r="J115">
-        <v>-25.092327117920004</v>
+        <v>-25.102639516194667</v>
       </c>
       <c r="K115">
-        <v>6.119988282521667</v>
+        <v>6.119984785715666</v>
       </c>
       <c r="L115">
-        <v>121.27658589680968</v>
+        <v>121.27198537190765</v>
       </c>
       <c r="M115">
         <v>5.7844444444444445</v>
       </c>
       <c r="N115">
-        <v>5.030415995174932</v>
+        <v>5.030086963502034</v>
       </c>
       <c r="O115" s="2">
-        <v>1.1421940410406406</v>
+        <v>1.1421394027571534</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -9000,22 +9000,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>-77.95453898112001</v>
+        <v>-77.93149820963534</v>
       </c>
       <c r="C116">
-        <v>18.599998474121335</v>
+        <v>18.599995930989333</v>
       </c>
       <c r="D116">
-        <v>30.72404607137033</v>
+        <v>30.724409739176334</v>
       </c>
       <c r="E116">
         <v>5.7844444444444445</v>
       </c>
       <c r="F116">
-        <v>5.013100122942445</v>
+        <v>5.013329786558203</v>
       </c>
       <c r="G116" s="2">
-        <v>1.5268435644098386</v>
+        <v>1.5273278199865759</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9028,22 +9028,22 @@
         </is>
       </c>
       <c r="J116">
-        <v>-25.649628321330002</v>
+        <v>-25.642045338948666</v>
       </c>
       <c r="K116">
-        <v>6.120010058085</v>
+        <v>6.120006084442</v>
       </c>
       <c r="L116">
-        <v>121.31058502197233</v>
+        <v>121.31202189127565</v>
       </c>
       <c r="M116">
         <v>5.7844444444444445</v>
       </c>
       <c r="N116">
-        <v>5.0130993329234075</v>
+        <v>5.01332865246826</v>
       </c>
       <c r="O116" s="2">
-        <v>1.1351551085217864</v>
+        <v>1.1352228435926774</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -9058,22 +9058,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>-61.526178995768326</v>
+        <v>-61.51789983113599</v>
       </c>
       <c r="C117">
         <v>18.59997113545733</v>
       </c>
       <c r="D117">
-        <v>30.864473978678337</v>
+        <v>30.86422602335633</v>
       </c>
       <c r="E117">
         <v>5.7844444444444445</v>
       </c>
       <c r="F117">
-        <v>5.229560967596806</v>
+        <v>5.2297051740787115</v>
       </c>
       <c r="G117" s="2">
-        <v>1.9741861020171456</v>
+        <v>1.9744811782477505</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9086,22 +9086,22 @@
         </is>
       </c>
       <c r="J117">
-        <v>-20.243912378946998</v>
+        <v>-20.241183598836333</v>
       </c>
       <c r="K117">
-        <v>6.119933287302667</v>
+        <v>6.1199248631793335</v>
       </c>
       <c r="L117">
-        <v>121.86480458577499</v>
+        <v>121.86382548014333</v>
       </c>
       <c r="M117">
         <v>5.7844444444444445</v>
       </c>
       <c r="N117">
-        <v>5.229560754058314</v>
+        <v>5.229703733774843</v>
       </c>
       <c r="O117" s="2">
-        <v>1.1930356296666178</v>
+        <v>1.1930864414103188</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -9526,13 +9526,13 @@
         </is>
       </c>
       <c r="B123">
-        <v>-66.2182411876153</v>
+        <v>-66.49143462075558</v>
       </c>
       <c r="C123">
-        <v>387.59333725408175</v>
+        <v>362.8155234661407</v>
       </c>
       <c r="D123" s="2">
-        <v>1.1440261897414763</v>
+        <v>1.7246582691226988</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -9545,13 +9545,13 @@
         </is>
       </c>
       <c r="G123">
-        <v>-21.787659152736435</v>
+        <v>-21.87755140848512</v>
       </c>
       <c r="H123">
-        <v>387.59333725408175</v>
+        <v>362.8155234661407</v>
       </c>
       <c r="I123" s="2">
-        <v>3.4769867486078736</v>
+        <v>5.241674463625814</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -9596,13 +9596,13 @@
         </is>
       </c>
       <c r="B124">
-        <v>-72.92718797389094</v>
+        <v>-73.16358277398334</v>
       </c>
       <c r="C124">
-        <v>387.59333725408175</v>
+        <v>362.8155234661407</v>
       </c>
       <c r="D124" s="2">
-        <v>1.0387813415261704</v>
+        <v>1.5673781708964556</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         </is>
       </c>
       <c r="G124">
-        <v>-23.995632429433044</v>
+        <v>-24.073413799738255</v>
       </c>
       <c r="H124">
-        <v>387.59333725408175</v>
+        <v>362.8155234661407</v>
       </c>
       <c r="I124" s="2">
-        <v>3.157049616426365</v>
+        <v>4.763553831561865</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="B125">
-        <v>-73.1681154413481</v>
+        <v>-73.57489603915427</v>
       </c>
       <c r="C125">
         <v>491.79</v>
       </c>
       <c r="D125" s="3">
-        <v>0.918952064142182</v>
+        <v>0.9138713655597739</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -9685,13 +9685,13 @@
         </is>
       </c>
       <c r="G125">
-        <v>-24.074543884354515</v>
+        <v>-24.20838321233366</v>
       </c>
       <c r="H125">
         <v>491.79</v>
       </c>
       <c r="I125" s="2">
-        <v>2.792908187054655</v>
+        <v>2.7774672155703466</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="B126">
-        <v>-72.747284230178</v>
+        <v>-72.80487964039108</v>
       </c>
       <c r="C126">
-        <v>387.59333725408175</v>
+        <v>362.8155234661407</v>
       </c>
       <c r="D126" s="2">
-        <v>1.0413502436400748</v>
+        <v>1.5751005030286103</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -9755,13 +9755,13 @@
         </is>
       </c>
       <c r="G126">
-        <v>-23.93611706756957</v>
+        <v>-23.95506459933124</v>
       </c>
       <c r="H126">
-        <v>387.59333725408175</v>
+        <v>362.8155234661407</v>
       </c>
       <c r="I126" s="2">
-        <v>3.1648993837805333</v>
+        <v>4.787088010930216</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="B127">
-        <v>-72.8618375583078</v>
+        <v>-73.26930388395937</v>
       </c>
       <c r="C127">
         <v>491.79</v>
       </c>
       <c r="D127" s="3">
-        <v>0.9228149188580784</v>
+        <v>0.9176829470184241</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -9825,13 +9825,13 @@
         </is>
       </c>
       <c r="G127">
-        <v>-23.973925351032513</v>
+        <v>-24.107997530643726</v>
       </c>
       <c r="H127">
         <v>491.79</v>
       </c>
       <c r="I127" s="2">
-        <v>2.804630019060457</v>
+        <v>2.789032586748607</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -9876,13 +9876,13 @@
         </is>
       </c>
       <c r="B128">
-        <v>-72.6994006691911</v>
+        <v>-72.75102589948524</v>
       </c>
       <c r="C128">
-        <v>387.59333725408175</v>
+        <v>362.8155234661407</v>
       </c>
       <c r="D128" s="2">
-        <v>1.0420361304209982</v>
+        <v>1.5762664667156097</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="G128">
-        <v>-23.920534804584495</v>
+        <v>-23.937519071634018</v>
       </c>
       <c r="H128">
-        <v>387.59333725408175</v>
+        <v>362.8155234661407</v>
       </c>
       <c r="I128" s="2">
-        <v>3.1669610556838683</v>
+        <v>4.790596811697474</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -9946,13 +9946,13 @@
         </is>
       </c>
       <c r="B129">
-        <v>-74.2133416088431</v>
+        <v>-74.41161868910268</v>
       </c>
       <c r="C129">
         <v>491.79</v>
       </c>
       <c r="D129" s="3">
-        <v>0.9060094756090107</v>
+        <v>0.9035953242079797</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -9965,13 +9965,13 @@
         </is>
       </c>
       <c r="G129">
-        <v>-24.418644099885476</v>
+        <v>-24.483886199761958</v>
       </c>
       <c r="H129">
         <v>491.79</v>
       </c>
       <c r="I129" s="2">
-        <v>2.7535513617865317</v>
+        <v>2.746213986032741</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -10016,13 +10016,13 @@
         </is>
       </c>
       <c r="B130">
-        <v>-76.23322758967643</v>
+        <v>-76.23844296081845</v>
       </c>
       <c r="C130">
         <v>491.79</v>
       </c>
       <c r="D130" s="3">
-        <v>0.8820037251489234</v>
+        <v>0.8819433884395594</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="G130">
-        <v>-25.08319830763531</v>
+        <v>-25.08491431222198</v>
       </c>
       <c r="H130">
         <v>491.79</v>
       </c>
       <c r="I130" s="2">
-        <v>2.6805987772999864</v>
+        <v>2.6804154033510224</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="B131">
-        <v>-68.90772643942142</v>
+        <v>-68.89444833091554</v>
       </c>
       <c r="C131">
         <v>491.79</v>
       </c>
       <c r="D131" s="3">
-        <v>0.9757685268187011</v>
+        <v>0.9759565878408824</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -10105,13 +10105,13 @@
         </is>
       </c>
       <c r="G131">
-        <v>-22.67279015592485</v>
+        <v>-22.66841855762845</v>
       </c>
       <c r="H131">
         <v>491.79</v>
       </c>
       <c r="I131" s="2">
-        <v>2.9655807799486764</v>
+        <v>2.9661526913880443</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -10484,16 +10484,16 @@
         </is>
       </c>
       <c r="B136">
-        <v>82841.66183943089</v>
+        <v>124656.32338853959</v>
       </c>
       <c r="C136">
-        <v>7.946163259608169</v>
+        <v>9.77653724016467</v>
       </c>
       <c r="D136">
-        <v>75.50813900966672</v>
+        <v>61.371422750279834</v>
       </c>
       <c r="E136">
-        <v>57.81932890503286</v>
+        <v>59.76105665571706</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10558,16 +10558,16 @@
         </is>
       </c>
       <c r="B137">
-        <v>82841.66183943089</v>
+        <v>124656.32338853959</v>
       </c>
       <c r="C137">
-        <v>7.946163259608169</v>
+        <v>9.77653724016467</v>
       </c>
       <c r="D137">
-        <v>75.50813900966672</v>
+        <v>61.371422750279834</v>
       </c>
       <c r="E137">
-        <v>57.81932890503286</v>
+        <v>59.76105665571706</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10706,16 +10706,16 @@
         </is>
       </c>
       <c r="B139">
-        <v>82841.66183943089</v>
+        <v>124656.32338853959</v>
       </c>
       <c r="C139">
-        <v>7.946163259608169</v>
+        <v>9.77653724016467</v>
       </c>
       <c r="D139">
-        <v>75.50813900966672</v>
+        <v>61.371422750279834</v>
       </c>
       <c r="E139">
-        <v>57.81932890503286</v>
+        <v>59.76105665571706</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10854,16 +10854,16 @@
         </is>
       </c>
       <c r="B141">
-        <v>82841.66183943089</v>
+        <v>124656.32338853959</v>
       </c>
       <c r="C141">
-        <v>7.946163259608169</v>
+        <v>9.77653724016467</v>
       </c>
       <c r="D141">
-        <v>75.50813900966672</v>
+        <v>61.371422750279834</v>
       </c>
       <c r="E141">
-        <v>57.81932890503286</v>
+        <v>59.76105665571706</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="B147" s="2">
-        <v>1.657138996173068</v>
+        <v>1.657175741031117</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="B148" s="2">
-        <v>1.1351551085217864</v>
+        <v>1.1352228435926774</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         </is>
       </c>
       <c r="B149" s="3">
-        <v>0.8820037251489234</v>
+        <v>0.8819433884395594</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="B150" s="3">
-        <v>0.8820037251489234</v>
+        <v>0.8819433884395594</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         </is>
       </c>
       <c r="B153">
-        <v>20.189088</v>
+        <v>20.138544</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>

--- a/calculation_python/outputs/Results_final.xlsx
+++ b/calculation_python/outputs/Results_final.xlsx
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C21">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C22">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C23">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C24">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C25">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C26">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2192,10 +2192,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C27">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C28">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C29">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>5.0</v>
+        <v>4.9</v>
       </c>
       <c r="C30">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="B32">
-        <v>2.1</v>
+        <v>2.0</v>
       </c>
       <c r="C32">
-        <v>55.0</v>
+        <v>48.0</v>
       </c>
       <c r="D32">
-        <v>11.371794871794872</v>
+        <v>9.078947368421053</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="B33">
-        <v>2.1</v>
+        <v>2.0</v>
       </c>
       <c r="C33">
-        <v>55.0</v>
+        <v>48.0</v>
       </c>
       <c r="D33">
-        <v>11.371794871794872</v>
+        <v>9.078947368421053</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B34">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="C34">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="D34">
-        <v>12.128063241106721</v>
+        <v>13.59656771799629</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2814,13 +2814,13 @@
         </is>
       </c>
       <c r="B35">
-        <v>2.1</v>
+        <v>2.0</v>
       </c>
       <c r="C35">
-        <v>55.0</v>
+        <v>48.0</v>
       </c>
       <c r="D35">
-        <v>11.371794871794872</v>
+        <v>9.078947368421053</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2890,13 +2890,13 @@
         </is>
       </c>
       <c r="B36">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="C36">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="D36">
-        <v>12.128063241106721</v>
+        <v>13.59656771799629</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="B37">
-        <v>2.1</v>
+        <v>2.0</v>
       </c>
       <c r="C37">
-        <v>55.0</v>
+        <v>48.0</v>
       </c>
       <c r="D37">
-        <v>11.371794871794872</v>
+        <v>9.078947368421053</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3042,13 +3042,13 @@
         </is>
       </c>
       <c r="B38">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="C38">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="D38">
-        <v>12.128063241106721</v>
+        <v>13.59656771799629</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="B39">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="C39">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="D39">
-        <v>12.128063241106721</v>
+        <v>13.59656771799629</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3194,13 +3194,13 @@
         </is>
       </c>
       <c r="B40">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="C40">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="D40">
-        <v>12.128063241106721</v>
+        <v>13.59656771799629</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="B46" s="2">
-        <v>4.294539485208779</v>
+        <v>4.223958179677957</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="E46" s="2">
-        <v>1.6875157757509338</v>
+        <v>1.6534985433824334</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="B47" s="2">
-        <v>3.6730805994301385</v>
+        <v>3.6164567816600233</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E47" s="2">
-        <v>1.6670271369762553</v>
+        <v>1.633724783056137</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="B48" s="2">
-        <v>4.070226023595548</v>
+        <v>4.004827677456054</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E48" s="2">
-        <v>1.6686408621969662</v>
+        <v>1.6352737609434735</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         </is>
       </c>
       <c r="B49" s="2">
-        <v>3.481713704492909</v>
+        <v>3.4231858463791562</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="E49" s="2">
-        <v>1.682659409012414</v>
+        <v>1.64861169515436</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="B50" s="2">
-        <v>3.5498401609169714</v>
+        <v>3.487665495367187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="E50" s="2">
-        <v>1.6647747740362473</v>
+        <v>1.6312152721234177</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="B51" s="2">
-        <v>3.615547258111587</v>
+        <v>3.558875757806426</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="E51" s="2">
-        <v>1.701527513301477</v>
+        <v>1.6675165754600607</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B52" s="2">
-        <v>3.5600560013789138</v>
+        <v>3.4878059294835357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="E52" s="2">
-        <v>1.6874119836051793</v>
+        <v>1.6539809772566858</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="B53" s="2">
-        <v>3.4938078534445367</v>
+        <v>3.4188285330801107</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="E53" s="2">
-        <v>1.6624609946202498</v>
+        <v>1.629003379474188</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="B54" s="2">
-        <v>3.5464433839054657</v>
+        <v>3.4576668586983645</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="E54" s="2">
-        <v>1.6855293650739018</v>
+        <v>1.6497747338544835</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="B55" s="2">
-        <v>3.514717127714317</v>
+        <v>3.424855316679993</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="E55" s="2">
-        <v>1.681147935189644</v>
+        <v>1.6457552667877215</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="B56" s="2">
-        <v>3.528771171420777</v>
+        <v>3.447248528531045</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="E56" s="2">
-        <v>1.6630291587106383</v>
+        <v>1.629240424673425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="B57" s="2">
-        <v>3.576240524551117</v>
+        <v>3.5045482106303307</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="E57" s="2">
-        <v>1.6897405122820959</v>
+        <v>1.6569727018879323</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="B58" s="2">
-        <v>3.5776794780537804</v>
+        <v>3.504091953991475</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="E58" s="2">
-        <v>1.6893991188567163</v>
+        <v>1.656355296107656</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="B59" s="2">
-        <v>3.5404254210684223</v>
+        <v>3.461249152805765</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="E59" s="2">
-        <v>1.6632024378091932</v>
+        <v>1.6294293517733112</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="B60" s="2">
-        <v>3.523021702996304</v>
+        <v>3.4345198609525918</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="E60" s="2">
-        <v>1.6817959788422372</v>
+        <v>1.6466004110830048</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="B61" s="2">
-        <v>3.5190275203731756</v>
+        <v>3.4279022704626496</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E61" s="2">
-        <v>1.6813713678724984</v>
+        <v>1.6457908562575874</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="B62" s="2">
-        <v>3.5467756990901034</v>
+        <v>3.470037166594312</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="E62" s="2">
-        <v>1.663251695154944</v>
+        <v>1.6295506358297556</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="B63" s="2">
-        <v>3.581402668130521</v>
+        <v>3.509318527277671</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="E63" s="2">
-        <v>1.690045449056631</v>
+        <v>1.6572084220066605</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="B64" s="2">
-        <v>3.5665198857137694</v>
+        <v>3.4913490132516087</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="E64" s="2">
-        <v>1.6883566372538423</v>
+        <v>1.655556462717312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="B65" s="2">
-        <v>3.5328351193910956</v>
+        <v>3.4471179574674227</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="E65" s="2">
-        <v>1.6634680426904453</v>
+        <v>1.6294727435893068</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="B66" s="2">
-        <v>3.519364335261394</v>
+        <v>3.4280910848450947</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="E66" s="2">
-        <v>1.6817633909275413</v>
+        <v>1.6466210185476664</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="B67" s="2">
-        <v>3.5155936415104048</v>
+        <v>3.4099513710116423</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="E67" s="2">
-        <v>1.6815367722666439</v>
+        <v>1.6471671552013907</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="B68" s="2">
-        <v>3.426995493140162</v>
+        <v>3.322398374713197</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="E68" s="2">
-        <v>1.659180123358753</v>
+        <v>1.6252258005089142</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="B69" s="2">
-        <v>3.479551564164482</v>
+        <v>3.372436620801657</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="E69" s="2">
-        <v>1.6763548332210474</v>
+        <v>1.641608028763246</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="B70" s="2">
-        <v>3.4930192748248414</v>
+        <v>3.3878184258041304</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="E70" s="2">
-        <v>1.6885501194476966</v>
+        <v>1.6543161246394338</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="B71" s="2">
-        <v>3.423815006785263</v>
+        <v>3.314353240038751</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="E71" s="2">
-        <v>1.657175741031117</v>
+        <v>1.622998710218532</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="B72" s="2">
-        <v>3.359111702685511</v>
+        <v>3.2565816892584616</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="E72" s="2">
-        <v>1.6680857389537442</v>
+        <v>1.633641784609632</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="B73" s="2">
-        <v>3.9737339091955555</v>
+        <v>3.8772297333462196</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="E73" s="2">
-        <v>1.65947628079372</v>
+        <v>1.6250522930651339</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="B74" s="2">
-        <v>3.599476716958905</v>
+        <v>3.515392254273092</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="E74" s="2">
-        <v>1.6631500871577718</v>
+        <v>1.6296307101069152</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="B75" s="2">
-        <v>4.2530161533825614</v>
+        <v>4.169366796372837</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="E75" s="2">
-        <v>1.6838837155031787</v>
+        <v>1.6507234679264537</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="B76" s="2">
-        <v>5.233671030157329</v>
+        <v>4.801755115440661</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="E76" s="2">
-        <v>16.49570322843346</v>
+        <v>15.108307027929905</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="B77" s="2">
-        <v>5.7869196584909615</v>
+        <v>5.306467805454812</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="E77" s="2">
-        <v>17.586069643532014</v>
+        <v>16.126158075243495</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="B78" s="2">
-        <v>5.200107458665923</v>
+        <v>4.772395958653132</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="E78" s="2">
-        <v>15.268142620286948</v>
+        <v>14.034441224929955</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="B79" s="2">
-        <v>5.1257002351411485</v>
+        <v>4.701771509240911</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="E79" s="2">
-        <v>15.51560719450454</v>
+        <v>14.253486561221308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="B80" s="2">
-        <v>4.9270893200272505</v>
+        <v>4.538791239210426</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="E80" s="2">
-        <v>14.972671698033828</v>
+        <v>13.792793498328667</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="B81" s="2">
-        <v>5.129495179995125</v>
+        <v>4.703972850617351</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="E81" s="2">
-        <v>15.653439291635081</v>
+        <v>14.33345382023492</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="B82" s="2">
-        <v>4.984452209156346</v>
+        <v>4.946845115554691</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="E82" s="2">
-        <v>15.118014966194307</v>
+        <v>15.015191797935449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="B83" s="2">
-        <v>5.032613512196029</v>
+        <v>4.929842509702396</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="E83" s="2">
-        <v>15.297291503145384</v>
+        <v>14.984927385367211</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="B84" s="2">
-        <v>4.986156778850298</v>
+        <v>4.94785961379399</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="E84" s="2">
-        <v>15.182809600877297</v>
+        <v>15.054831811560872</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="B85" s="2">
-        <v>5.165918136448703</v>
+        <v>4.75805351243442</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="E85" s="2">
-        <v>15.71023989335279</v>
+        <v>14.469078776324821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="B86" s="2">
-        <v>5.101030712900475</v>
+        <v>4.718449110262779</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="E86" s="2">
-        <v>15.503007655811183</v>
+        <v>14.340265874656296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="B87" s="2">
-        <v>5.165273269807008</v>
+        <v>4.757505961773383</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="E87" s="2">
-        <v>15.687645560757037</v>
+        <v>14.450014647435022</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="B88" s="2">
-        <v>4.981449185250068</v>
+        <v>4.9438130571580325</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="E88" s="2">
-        <v>15.138962630409768</v>
+        <v>15.026678942148536</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="B89" s="2">
-        <v>5.02728203485955</v>
+        <v>4.928584975783267</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="E89" s="2">
-        <v>15.278506714153767</v>
+        <v>14.978527252824287</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="B90" s="2">
-        <v>4.981475352561514</v>
+        <v>4.943701550839108</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="E90" s="2">
-        <v>15.139891175907504</v>
+        <v>15.022951554992465</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="B91" s="2">
-        <v>5.16935707939105</v>
+        <v>4.761761561895916</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="E91" s="2">
-        <v>15.699231617631261</v>
+        <v>14.464679487767885</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="B92" s="2">
-        <v>5.122614445027513</v>
+        <v>4.744699410052975</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="E92" s="2">
-        <v>15.568501633359912</v>
+        <v>14.419928202372416</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="B93" s="2">
-        <v>5.170103630949604</v>
+        <v>4.762251036536406</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="E93" s="2">
-        <v>15.724604615458013</v>
+        <v>14.480794349368402</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="B94" s="2">
-        <v>4.97366834601145</v>
+        <v>4.981173644129183</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="E94" s="2">
-        <v>15.089237191805108</v>
+        <v>15.152834840568365</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="B95" s="2">
-        <v>4.999293203769039</v>
+        <v>4.978160168608262</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="E95" s="2">
-        <v>15.194179631312323</v>
+        <v>15.129937137738048</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="B96" s="2">
-        <v>4.975335181877686</v>
+        <v>4.98039738018037</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="E96" s="2">
-        <v>15.148426055178707</v>
+        <v>15.122930215385207</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="B97" s="2">
-        <v>4.9307134860945006</v>
+        <v>4.973659295958738</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="E97" s="2">
-        <v>15.028317925993223</v>
+        <v>15.162999636079554</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="B98" s="2">
-        <v>4.78489784595573</v>
+        <v>4.8120438128395735</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="E98" s="2">
-        <v>14.542670305074076</v>
+        <v>14.625166409039673</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="B99" s="2">
-        <v>4.928137542623586</v>
+        <v>4.970835691488778</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="E99" s="2">
-        <v>14.935681370128268</v>
+        <v>15.061347370126835</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="B100" s="2">
-        <v>5.23451175031139</v>
+        <v>5.264161156973303</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="E100" s="2">
-        <v>15.404025749596126</v>
+        <v>15.45334664133306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="B101" s="2">
-        <v>5.776155777899696</v>
+        <v>5.831890036632843</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="E101" s="2">
-        <v>17.555245132299873</v>
+        <v>17.72463926557494</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="B102" s="2">
-        <v>5.2658482003530445</v>
+        <v>5.298133500802496</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="E102" s="2">
-        <v>16.549725707429914</v>
+        <v>16.69551178585162</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8536,22 +8536,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>-59.59139251708999</v>
+        <v>-60.32433700561499</v>
       </c>
       <c r="C108">
-        <v>18.600114186605</v>
+        <v>18.97970835367833</v>
       </c>
       <c r="D108">
-        <v>30.770037333170666</v>
+        <v>31.40196164449067</v>
       </c>
       <c r="E108">
         <v>5.7844444444444445</v>
       </c>
       <c r="F108">
-        <v>5.26459119230698</v>
+        <v>5.273587161525374</v>
       </c>
       <c r="G108" s="2">
-        <v>2.046065081166741</v>
+        <v>1.9318466745402407</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8564,22 +8564,22 @@
         </is>
       </c>
       <c r="J108">
-        <v>-19.607909838358665</v>
+        <v>-19.849076588948332</v>
       </c>
       <c r="K108">
-        <v>6.120551109314</v>
+        <v>6.245459079742333</v>
       </c>
       <c r="L108">
-        <v>121.49289194742833</v>
+        <v>123.98799387613933</v>
       </c>
       <c r="M108">
         <v>5.7844444444444445</v>
       </c>
       <c r="N108">
-        <v>5.2646612879452235</v>
+        <v>5.273657880922645</v>
       </c>
       <c r="O108" s="2">
-        <v>1.2073604371471607</v>
+        <v>1.0822937653546478</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -8594,22 +8594,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>-73.85754903157567</v>
+        <v>-74.943916320801</v>
       </c>
       <c r="C109">
-        <v>18.600112915039002</v>
+        <v>18.979705174764</v>
       </c>
       <c r="D109">
-        <v>30.533096949259328</v>
+        <v>31.163029988607</v>
       </c>
       <c r="E109">
         <v>5.7844444444444445</v>
       </c>
       <c r="F109">
-        <v>5.056587302123366</v>
+        <v>5.061278771268094</v>
       </c>
       <c r="G109" s="2">
-        <v>1.6199720620847442</v>
+        <v>1.527242546571286</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8622,22 +8622,22 @@
         </is>
       </c>
       <c r="J109">
-        <v>-24.301781336466668</v>
+        <v>-24.65924517313633</v>
       </c>
       <c r="K109">
-        <v>6.120554288228666</v>
+        <v>6.245464324951333</v>
       </c>
       <c r="L109">
-        <v>120.557861328125</v>
+        <v>123.04509989420568</v>
       </c>
       <c r="M109">
         <v>5.7844444444444445</v>
       </c>
       <c r="N109">
-        <v>5.056648711509736</v>
+        <v>5.061340483811615</v>
       </c>
       <c r="O109" s="2">
-        <v>1.162364311401517</v>
+        <v>1.0442060684019623</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -8652,22 +8652,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>-74.34720357259134</v>
+        <v>-76.13510131835966</v>
       </c>
       <c r="C110">
-        <v>18.599923451741667</v>
+        <v>18.979515711466664</v>
       </c>
       <c r="D110">
-        <v>30.613504409790004</v>
+        <v>31.248978932698662</v>
       </c>
       <c r="E110">
         <v>5.7844444444444445</v>
       </c>
       <c r="F110">
-        <v>5.051088601320718</v>
+        <v>5.048150197069647</v>
       </c>
       <c r="G110" s="2">
-        <v>1.6078257237738784</v>
+        <v>1.5008725023146414</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8680,22 +8680,22 @@
         </is>
       </c>
       <c r="J110">
-        <v>-24.462598164876667</v>
+        <v>-25.050894419352332</v>
       </c>
       <c r="K110">
-        <v>6.1196630795796665</v>
+        <v>6.244550704956334</v>
       </c>
       <c r="L110">
-        <v>120.87309773763033</v>
+        <v>123.38216908772766</v>
       </c>
       <c r="M110">
         <v>5.7844444444444445</v>
       </c>
       <c r="N110">
-        <v>5.051047483500603</v>
+        <v>5.048108042689617</v>
       </c>
       <c r="O110" s="2">
-        <v>1.1556788098364836</v>
+        <v>1.0357071392488881</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -8710,22 +8710,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>-74.10671742757168</v>
+        <v>-75.97364044189467</v>
       </c>
       <c r="C111">
-        <v>18.599953333537</v>
+        <v>18.979544321695997</v>
       </c>
       <c r="D111">
-        <v>30.624097188313666</v>
+        <v>31.255163828531995</v>
       </c>
       <c r="E111">
         <v>5.7844444444444445</v>
       </c>
       <c r="F111">
-        <v>5.053775805161672</v>
+        <v>5.049901790704045</v>
       </c>
       <c r="G111" s="2">
-        <v>1.613399088217573</v>
+        <v>1.5042672092328575</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8738,22 +8738,22 @@
         </is>
       </c>
       <c r="J111">
-        <v>-24.383182525635</v>
+        <v>-24.997454961140996</v>
       </c>
       <c r="K111">
-        <v>6.119788010915</v>
+        <v>6.244683424631666</v>
       </c>
       <c r="L111">
-        <v>120.91515858968067</v>
+        <v>123.40682474772133</v>
       </c>
       <c r="M111">
         <v>5.7844444444444445</v>
       </c>
       <c r="N111">
-        <v>5.053759948278408</v>
+        <v>5.049886178624456</v>
       </c>
       <c r="O111" s="2">
-        <v>1.1560130842732599</v>
+        <v>1.035921709111886</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -8768,22 +8768,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>-73.86626180013033</v>
+        <v>-75.70033009847</v>
       </c>
       <c r="C112">
-        <v>18.599972407023</v>
+        <v>18.979562123616667</v>
       </c>
       <c r="D112">
-        <v>30.622621536255</v>
+        <v>31.254144668579002</v>
       </c>
       <c r="E112">
         <v>5.7844444444444445</v>
       </c>
       <c r="F112">
-        <v>5.0564825656140435</v>
+        <v>5.052885261060473</v>
       </c>
       <c r="G112" s="2">
-        <v>1.6190998471408604</v>
+        <v>1.5101303148908247</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8796,22 +8796,22 @@
         </is>
       </c>
       <c r="J112">
-        <v>-24.304182688395333</v>
+        <v>-24.907646814981998</v>
       </c>
       <c r="K112">
-        <v>6.119893391927</v>
+        <v>6.244789282480666</v>
       </c>
       <c r="L112">
-        <v>120.90924835205065</v>
+        <v>123.40272521972666</v>
       </c>
       <c r="M112">
         <v>5.7844444444444445</v>
       </c>
       <c r="N112">
-        <v>5.05647614256255</v>
+        <v>5.05287890831738</v>
       </c>
       <c r="O112" s="2">
-        <v>1.1570592508150843</v>
+        <v>1.0368865554673732</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -8826,22 +8826,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>-73.79817199707</v>
+        <v>-75.61210378011066</v>
       </c>
       <c r="C113">
-        <v>18.599981307983665</v>
+        <v>18.979574839274</v>
       </c>
       <c r="D113">
-        <v>30.621356964111335</v>
+        <v>31.253635406494332</v>
       </c>
       <c r="E113">
         <v>5.7844444444444445</v>
       </c>
       <c r="F113">
-        <v>5.057252930087406</v>
+        <v>5.05385401161036</v>
       </c>
       <c r="G113" s="2">
-        <v>1.6207277957734516</v>
+        <v>1.5120341078421815</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8854,22 +8854,22 @@
         </is>
       </c>
       <c r="J113">
-        <v>-24.281985600789668</v>
+        <v>-24.878818511963</v>
       </c>
       <c r="K113">
-        <v>6.119934717814333</v>
+        <v>6.244825522104667</v>
       </c>
       <c r="L113">
-        <v>120.90442657470733</v>
+        <v>123.40089416503935</v>
       </c>
       <c r="M113">
         <v>5.7844444444444445</v>
       </c>
       <c r="N113">
-        <v>5.057244637132175</v>
+        <v>5.053845209101098</v>
       </c>
       <c r="O113" s="2">
-        <v>1.1574009172606454</v>
+        <v>1.0372035129194788</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -8884,22 +8884,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>-74.11598459879568</v>
+        <v>-76.09193166097</v>
       </c>
       <c r="C114">
-        <v>18.599973678589</v>
+        <v>18.97956720987933</v>
       </c>
       <c r="D114">
-        <v>30.625796000163003</v>
+        <v>31.256167093912666</v>
       </c>
       <c r="E114">
         <v>5.7844444444444445</v>
       </c>
       <c r="F114">
-        <v>5.053672837177586</v>
+        <v>5.0486195758006</v>
       </c>
       <c r="G114" s="2">
-        <v>1.6131683742099063</v>
+        <v>1.501740093118191</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -8912,22 +8912,22 @@
         </is>
       </c>
       <c r="J114">
-        <v>-24.386686325073327</v>
+        <v>-25.036827087402333</v>
       </c>
       <c r="K114">
-        <v>6.119884808858</v>
+        <v>6.244777361552</v>
       </c>
       <c r="L114">
-        <v>120.92235056559267</v>
+        <v>123.41131846110034</v>
       </c>
       <c r="M114">
         <v>5.7844444444444445</v>
       </c>
       <c r="N114">
-        <v>5.053653726908456</v>
+        <v>5.048600554286684</v>
       </c>
       <c r="O114" s="2">
-        <v>1.1558639826643111</v>
+        <v>1.035464343596476</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -8942,22 +8942,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>-76.29179382324233</v>
+        <v>-79.17384592692066</v>
       </c>
       <c r="C115">
-        <v>18.599988937377997</v>
+        <v>18.979579925537333</v>
       </c>
       <c r="D115">
-        <v>30.714287439981998</v>
+        <v>31.350217819213665</v>
       </c>
       <c r="E115">
         <v>5.7844444444444445</v>
       </c>
       <c r="F115">
-        <v>5.030094154526985</v>
+        <v>5.016749770417856</v>
       </c>
       <c r="G115" s="2">
-        <v>1.5628487411623977</v>
+        <v>1.4383191847816408</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -8970,22 +8970,22 @@
         </is>
       </c>
       <c r="J115">
-        <v>-25.102639516194667</v>
+        <v>-26.05091476440433</v>
       </c>
       <c r="K115">
-        <v>6.119984785715666</v>
+        <v>6.244877974192334</v>
       </c>
       <c r="L115">
-        <v>121.27198537190765</v>
+        <v>123.78288777669266</v>
       </c>
       <c r="M115">
         <v>5.7844444444444445</v>
       </c>
       <c r="N115">
-        <v>5.030086963502034</v>
+        <v>5.016742792692896</v>
       </c>
       <c r="O115" s="2">
-        <v>1.1421394027571534</v>
+        <v>1.020497721835162</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -9000,22 +9000,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>-77.93149820963534</v>
+        <v>-80.90717824300134</v>
       </c>
       <c r="C116">
-        <v>18.599995930989333</v>
+        <v>18.979590098063003</v>
       </c>
       <c r="D116">
-        <v>30.724409739176334</v>
+        <v>31.359082539876333</v>
       </c>
       <c r="E116">
         <v>5.7844444444444445</v>
       </c>
       <c r="F116">
-        <v>5.013329786558203</v>
+        <v>5.000054587261049</v>
       </c>
       <c r="G116" s="2">
-        <v>1.5273278199865759</v>
+        <v>1.4052214291995233</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9028,22 +9028,22 @@
         </is>
       </c>
       <c r="J116">
-        <v>-25.642045338948666</v>
+        <v>-26.621129353841003</v>
       </c>
       <c r="K116">
-        <v>6.120006084442</v>
+        <v>6.244911670685</v>
       </c>
       <c r="L116">
-        <v>121.31202189127565</v>
+        <v>123.81796010335266</v>
       </c>
       <c r="M116">
         <v>5.7844444444444445</v>
       </c>
       <c r="N116">
-        <v>5.01332865246826</v>
+        <v>5.000054675366959</v>
       </c>
       <c r="O116" s="2">
-        <v>1.1352228435926774</v>
+        <v>1.014480005009336</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -9058,22 +9058,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>-61.51789983113599</v>
+        <v>-63.055662790934</v>
       </c>
       <c r="C117">
-        <v>18.59997113545733</v>
+        <v>18.979565302531334</v>
       </c>
       <c r="D117">
-        <v>30.86422602335633</v>
+        <v>31.499007542928332</v>
       </c>
       <c r="E117">
         <v>5.7844444444444445</v>
       </c>
       <c r="F117">
-        <v>5.2297051740787115</v>
+        <v>5.22491184629002</v>
       </c>
       <c r="G117" s="2">
-        <v>1.9744811782477505</v>
+        <v>1.8392283009645167</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9086,22 +9086,22 @@
         </is>
       </c>
       <c r="J117">
-        <v>-20.241183598836333</v>
+        <v>-20.747158050537</v>
       </c>
       <c r="K117">
-        <v>6.1199248631793335</v>
+        <v>6.2448258399963334</v>
       </c>
       <c r="L117">
-        <v>121.86382548014333</v>
+        <v>124.37018839518232</v>
       </c>
       <c r="M117">
         <v>5.7844444444444445</v>
       </c>
       <c r="N117">
-        <v>5.229703733774843</v>
+        <v>5.224910740958874</v>
       </c>
       <c r="O117" s="2">
-        <v>1.1930864414103188</v>
+        <v>1.0670185201920448</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -9526,13 +9526,13 @@
         </is>
       </c>
       <c r="B123">
-        <v>-66.49143462075558</v>
+        <v>-68.53707958115898</v>
       </c>
       <c r="C123">
-        <v>362.8155234661407</v>
+        <v>381.41891422091203</v>
       </c>
       <c r="D123" s="2">
-        <v>1.7246582691226988</v>
+        <v>1.1362729011771808</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -9545,13 +9545,13 @@
         </is>
       </c>
       <c r="G123">
-        <v>-21.87755140848512</v>
+        <v>-22.55062284959625</v>
       </c>
       <c r="H123">
-        <v>362.8155234661407</v>
+        <v>381.41891422091203</v>
       </c>
       <c r="I123" s="2">
-        <v>5.241674463625814</v>
+        <v>3.4534224075894713</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -9596,13 +9596,13 @@
         </is>
       </c>
       <c r="B124">
-        <v>-73.16358277398334</v>
+        <v>-75.70906872051997</v>
       </c>
       <c r="C124">
-        <v>362.8155234661407</v>
+        <v>381.41891422091203</v>
       </c>
       <c r="D124" s="2">
-        <v>1.5673781708964556</v>
+        <v>1.028632732775741</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         </is>
       </c>
       <c r="G124">
-        <v>-24.073413799738255</v>
+        <v>-24.910967697425033</v>
       </c>
       <c r="H124">
-        <v>362.8155234661407</v>
+        <v>381.41891422091203</v>
       </c>
       <c r="I124" s="2">
-        <v>4.763553831561865</v>
+        <v>3.1262063842644183</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="B125">
-        <v>-73.57489603915427</v>
+        <v>-75.24540159471834</v>
       </c>
       <c r="C125">
         <v>491.79</v>
       </c>
-      <c r="D125" s="3">
-        <v>0.9138713655597739</v>
+      <c r="D125" s="2">
+        <v>1.0446505872126564</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -9685,13 +9685,13 @@
         </is>
       </c>
       <c r="G125">
-        <v>-24.20838321233366</v>
+        <v>-24.758037136397153</v>
       </c>
       <c r="H125">
         <v>491.79</v>
       </c>
       <c r="I125" s="2">
-        <v>2.7774672155703466</v>
+        <v>3.174934770794736</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="B126">
-        <v>-72.80487964039108</v>
+        <v>-75.58550920850834</v>
       </c>
       <c r="C126">
-        <v>362.8155234661407</v>
+        <v>381.41891422091203</v>
       </c>
       <c r="D126" s="2">
-        <v>1.5751005030286103</v>
+        <v>1.0303142370724223</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -9755,13 +9755,13 @@
         </is>
       </c>
       <c r="G126">
-        <v>-23.95506459933124</v>
+        <v>-24.869978260145785</v>
       </c>
       <c r="H126">
-        <v>362.8155234661407</v>
+        <v>381.41891422091203</v>
       </c>
       <c r="I126" s="2">
-        <v>4.787088010930216</v>
+        <v>3.131358839130659</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="B127">
-        <v>-73.26930388395937</v>
+        <v>-74.92962877452777</v>
       </c>
       <c r="C127">
         <v>491.79</v>
       </c>
-      <c r="D127" s="3">
-        <v>0.9176829470184241</v>
+      <c r="D127" s="2">
+        <v>1.0490530147627848</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -9825,13 +9825,13 @@
         </is>
       </c>
       <c r="G127">
-        <v>-24.107997530643726</v>
+        <v>-24.654295833266346</v>
       </c>
       <c r="H127">
         <v>491.79</v>
       </c>
       <c r="I127" s="2">
-        <v>2.789032586748607</v>
+        <v>3.1882943845798977</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -9876,13 +9876,13 @@
         </is>
       </c>
       <c r="B128">
-        <v>-72.75102589948524</v>
+        <v>-75.5560038771397</v>
       </c>
       <c r="C128">
-        <v>362.8155234661407</v>
+        <v>381.41891422091203</v>
       </c>
       <c r="D128" s="2">
-        <v>1.5762664667156097</v>
+        <v>1.0307165844891555</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="G128">
-        <v>-23.937519071634018</v>
+        <v>-24.86044907852603</v>
       </c>
       <c r="H128">
-        <v>362.8155234661407</v>
+        <v>381.41891422091203</v>
       </c>
       <c r="I128" s="2">
-        <v>4.790596811697474</v>
+        <v>3.1325591105738835</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -9946,13 +9946,13 @@
         </is>
       </c>
       <c r="B129">
-        <v>-74.41161868910268</v>
+        <v>-76.4238734117472</v>
       </c>
       <c r="C129">
         <v>491.79</v>
       </c>
-      <c r="D129" s="3">
-        <v>0.9035953242079797</v>
+      <c r="D129" s="2">
+        <v>1.0285418607020274</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -9965,13 +9965,13 @@
         </is>
       </c>
       <c r="G129">
-        <v>-24.483886199761958</v>
+        <v>-25.145979617108726</v>
       </c>
       <c r="H129">
         <v>491.79</v>
       </c>
       <c r="I129" s="2">
-        <v>2.746213986032741</v>
+        <v>3.1259531009678216</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -10016,13 +10016,13 @@
         </is>
       </c>
       <c r="B130">
-        <v>-76.23844296081845</v>
+        <v>-78.54876694729624</v>
       </c>
       <c r="C130">
         <v>491.79</v>
       </c>
-      <c r="D130" s="3">
-        <v>0.8819433884395594</v>
+      <c r="D130" s="2">
+        <v>1.0007178472160647</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="G130">
-        <v>-25.08491431222198</v>
+        <v>-25.84508223008113</v>
       </c>
       <c r="H130">
         <v>491.79</v>
       </c>
       <c r="I130" s="2">
-        <v>2.6804154033510224</v>
+        <v>3.0413968994645337</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="B131">
-        <v>-68.89444833091554</v>
+        <v>-70.67446780727697</v>
       </c>
       <c r="C131">
         <v>491.79</v>
       </c>
-      <c r="D131" s="3">
-        <v>0.9759565878408824</v>
+      <c r="D131" s="2">
+        <v>1.1122142889752489</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -10105,13 +10105,13 @@
         </is>
       </c>
       <c r="G131">
-        <v>-22.66841855762845</v>
+        <v>-23.254098556501937</v>
       </c>
       <c r="H131">
         <v>491.79</v>
       </c>
       <c r="I131" s="2">
-        <v>2.9661526913880443</v>
+        <v>3.38027091310303</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -10484,16 +10484,16 @@
         </is>
       </c>
       <c r="B136">
-        <v>124656.32338853959</v>
+        <v>82110.7708168643</v>
       </c>
       <c r="C136">
-        <v>9.77653724016467</v>
+        <v>8.056655649243401</v>
       </c>
       <c r="D136">
-        <v>61.371422750279834</v>
+        <v>74.47258839421117</v>
       </c>
       <c r="E136">
-        <v>59.76105665571706</v>
+        <v>58.2854408016979</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10558,16 +10558,16 @@
         </is>
       </c>
       <c r="B137">
-        <v>124656.32338853959</v>
+        <v>82110.7708168643</v>
       </c>
       <c r="C137">
-        <v>9.77653724016467</v>
+        <v>8.056655649243401</v>
       </c>
       <c r="D137">
-        <v>61.371422750279834</v>
+        <v>74.47258839421117</v>
       </c>
       <c r="E137">
-        <v>59.76105665571706</v>
+        <v>58.2854408016979</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10632,13 +10632,13 @@
         </is>
       </c>
       <c r="B138">
-        <v>69653.87557267422</v>
+        <v>79038.10244745466</v>
       </c>
       <c r="C138">
-        <v>7.486141696402191</v>
+        <v>8.094242066274209</v>
       </c>
       <c r="D138">
-        <v>80.14809555212635</v>
+        <v>74.12676753268646</v>
       </c>
       <c r="E138">
         <v>51.33001028308949</v>
@@ -10706,16 +10706,16 @@
         </is>
       </c>
       <c r="B139">
-        <v>124656.32338853959</v>
+        <v>82110.7708168643</v>
       </c>
       <c r="C139">
-        <v>9.77653724016467</v>
+        <v>8.056655649243401</v>
       </c>
       <c r="D139">
-        <v>61.371422750279834</v>
+        <v>74.47258839421117</v>
       </c>
       <c r="E139">
-        <v>59.76105665571706</v>
+        <v>58.2854408016979</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10780,13 +10780,13 @@
         </is>
       </c>
       <c r="B140">
-        <v>69653.87557267422</v>
+        <v>79038.10244745466</v>
       </c>
       <c r="C140">
-        <v>7.486141696402191</v>
+        <v>8.094242066274209</v>
       </c>
       <c r="D140">
-        <v>80.14809555212635</v>
+        <v>74.12676753268646</v>
       </c>
       <c r="E140">
         <v>51.33001028308949</v>
@@ -10854,16 +10854,16 @@
         </is>
       </c>
       <c r="B141">
-        <v>124656.32338853959</v>
+        <v>82110.7708168643</v>
       </c>
       <c r="C141">
-        <v>9.77653724016467</v>
+        <v>8.056655649243401</v>
       </c>
       <c r="D141">
-        <v>61.371422750279834</v>
+        <v>74.47258839421117</v>
       </c>
       <c r="E141">
-        <v>59.76105665571706</v>
+        <v>58.2854408016979</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10928,13 +10928,13 @@
         </is>
       </c>
       <c r="B142">
-        <v>69653.87557267422</v>
+        <v>79038.10244745466</v>
       </c>
       <c r="C142">
-        <v>7.486141696402191</v>
+        <v>8.094242066274209</v>
       </c>
       <c r="D142">
-        <v>80.14809555212635</v>
+        <v>74.12676753268646</v>
       </c>
       <c r="E142">
         <v>51.33001028308949</v>
@@ -11002,13 +11002,13 @@
         </is>
       </c>
       <c r="B143">
-        <v>69653.87557267422</v>
+        <v>79038.10244745466</v>
       </c>
       <c r="C143">
-        <v>7.486141696402191</v>
+        <v>8.094242066274209</v>
       </c>
       <c r="D143">
-        <v>80.14809555212635</v>
+        <v>74.12676753268646</v>
       </c>
       <c r="E143">
         <v>51.33001028308949</v>
@@ -11076,13 +11076,13 @@
         </is>
       </c>
       <c r="B144">
-        <v>69653.87557267422</v>
+        <v>79038.10244745466</v>
       </c>
       <c r="C144">
-        <v>7.486141696402191</v>
+        <v>8.094242066274209</v>
       </c>
       <c r="D144">
-        <v>80.14809555212635</v>
+        <v>74.12676753268646</v>
       </c>
       <c r="E144">
         <v>51.33001028308949</v>
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="B147" s="2">
-        <v>1.657175741031117</v>
+        <v>1.622998710218532</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         </is>
       </c>
       <c r="B148" s="2">
-        <v>1.1352228435926774</v>
+        <v>1.014480005009336</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -11473,8 +11473,8 @@
           <t>Minimum allover column buckling RF [-]</t>
         </is>
       </c>
-      <c r="B149" s="3">
-        <v>0.8819433884395594</v>
+      <c r="B149" s="2">
+        <v>1.0007178472160647</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -11553,8 +11553,8 @@
           <t>Minimum allover RF [-]</t>
         </is>
       </c>
-      <c r="B150" s="3">
-        <v>0.8819433884395594</v>
+      <c r="B150" s="2">
+        <v>1.0007178472160647</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         </is>
       </c>
       <c r="B153">
-        <v>20.138544</v>
+        <v>19.556478000000006</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>

--- a/calculation_python/outputs/Results_final.xlsx
+++ b/calculation_python/outputs/Results_final.xlsx
@@ -2592,7 +2592,7 @@
         <v>48.0</v>
       </c>
       <c r="D32">
-        <v>9.078947368421053</v>
+        <v>-9.078947368421053</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>48.0</v>
       </c>
       <c r="D33">
-        <v>9.078947368421053</v>
+        <v>-9.078947368421053</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>31.0</v>
       </c>
       <c r="D34">
-        <v>13.59656771799629</v>
+        <v>-13.59656771799629</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>48.0</v>
       </c>
       <c r="D35">
-        <v>9.078947368421053</v>
+        <v>-9.078947368421053</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>31.0</v>
       </c>
       <c r="D36">
-        <v>13.59656771799629</v>
+        <v>-13.59656771799629</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>48.0</v>
       </c>
       <c r="D37">
-        <v>9.078947368421053</v>
+        <v>-9.078947368421053</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>31.0</v>
       </c>
       <c r="D38">
-        <v>13.59656771799629</v>
+        <v>-13.59656771799629</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>31.0</v>
       </c>
       <c r="D39">
-        <v>13.59656771799629</v>
+        <v>-13.59656771799629</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>31.0</v>
       </c>
       <c r="D40">
-        <v>13.59656771799629</v>
+        <v>-13.59656771799629</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
